--- a/28388motherboard/TMS320F28388D_PinMap.xlsx
+++ b/28388motherboard/TMS320F28388D_PinMap.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Yan Zhengzhang\Desktop\377D工程重铸\28388d\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\codefile\28388Board\mmlab-12PhaseDrive-388Slave\28388motherboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{C0D457CD-6888-4406-82CE-DF3DA90DEFEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFC5EB73-A524-43D9-8898-FF984B8FD7DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-16740" yWindow="0" windowWidth="16845" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-19305" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PinMap" sheetId="1" r:id="rId1"/>
@@ -21,12 +21,11 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">PinMap!$A$1:$J$170</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
-  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1906" uniqueCount="837">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1908" uniqueCount="838">
   <si>
     <t>Comment（备注）</t>
   </si>
@@ -2455,10 +2454,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>DI-1-DSP-3.3V</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>DI-2-DSP-3.3V</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -2475,68 +2470,191 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>MQEP2A</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MQEP2B</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MQEP2Z</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>核心板for电压监测</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ADC_DO_W_4</t>
+  </si>
+  <si>
+    <t>ADC_DO_W_3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ADC_DO_U_2/ADC_DO_V_4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ADC_DO_U_1/ADC_DO_V_3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>逆变器4</t>
+  </si>
+  <si>
+    <t>逆变器4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>逆变器3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DSP_PWM4~{_ENABLE}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DSP_Discharge1_EN</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DSP_Discharge3_EN</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DSP_Discharge4_EN</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DSP_PWM1_~{FAULT}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DSP_PWM3_~{FAULT}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DSP_PWM4_~{FAULT}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DSP_Temperature2</t>
+  </si>
+  <si>
+    <t>DSP_Temperature4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DSP_Temperature3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HALL1_UY</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HALL1_WY</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MCU_485D_1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MCU_485R_1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>485_RTS_1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>485_RTS_2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MCU_485D_2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MCU_485R_2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HALL1_VY</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>485_RTS_4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MCU_485D_4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MCU_485R_4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MCU_485D_3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MCU_485R_3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DSP_Temperature1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DSP_Discharge2_EN</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MQEP1Z</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hall</t>
+  </si>
+  <si>
+    <t>HALL2_U</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HALL2_V</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HALL2_W</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DSP_PWM2~{_ENABLE}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DSP_PWM2_~{FAULT}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>eQEP</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MQEP1B</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>MQEP1A</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>MQEP1B</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>MQEP1Z</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>MQEP2A</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>MQEP2B</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>MQEP2Z</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>核心板for电压监测</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>ADC_DO_W_4</t>
-  </si>
-  <si>
-    <t>ADC_DO_W_3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ADC_DO_U_2/ADC_DO_V_4</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>ADC_DO_U_1/ADC_DO_V_3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>逆变器4</t>
-  </si>
-  <si>
-    <t>逆变器4</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>逆变器3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>DSP_PWM1~{_ENABLE}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>DSP_PWM2~{_ENABLE}</t>
+    <t>DSP_Discharge3_EN</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -2544,121 +2662,7 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>DSP_PWM4~{_ENABLE}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>DSP_Discharge1_EN</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>DSP_Discharge2_EN</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>DSP_Discharge3_EN</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>DSP_Discharge4_EN</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>DSP_PWM1_~{FAULT}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>DSP_PWM2_~{FAULT}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>DSP_PWM3_~{FAULT}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>DSP_PWM4_~{FAULT}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>DSP_Temperature1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>DSP_Temperature2</t>
-  </si>
-  <si>
-    <t>DSP_Temperature4</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>DSP_Temperature3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>HALL1_UY</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>HALL1_WY</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>HALL2_UY</t>
-  </si>
-  <si>
-    <t>HALL2_VY</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>HALL2_WY</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>MCU_485D_1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>MCU_485R_1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>485_RTS_1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>485_RTS_2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>MCU_485D_2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>MCU_485R_2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>HALL1_VY</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>485_RTS_4</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>MCU_485D_4</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>MCU_485R_4</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>MCU_485D_3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>MCU_485R_3</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -4541,7 +4545,7 @@
         <v>9</v>
       </c>
       <c r="E42" t="s">
-        <v>784</v>
+        <v>830</v>
       </c>
       <c r="F42" t="str">
         <f t="shared" si="2"/>
@@ -4576,7 +4580,7 @@
         <v>9</v>
       </c>
       <c r="E43" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="F43" t="str">
         <f t="shared" si="2"/>
@@ -4607,9 +4611,15 @@
 )</f>
         <v/>
       </c>
+      <c r="D44" t="s">
+        <v>826</v>
+      </c>
+      <c r="E44" t="s">
+        <v>829</v>
+      </c>
       <c r="F44" t="str">
         <f t="shared" si="2"/>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="J44">
         <f t="shared" si="3"/>
@@ -4831,7 +4841,7 @@
         <v>770</v>
       </c>
       <c r="E50" t="s">
-        <v>825</v>
+        <v>811</v>
       </c>
       <c r="F50" t="str">
         <f t="shared" si="2"/>
@@ -4868,7 +4878,7 @@
         <v>770</v>
       </c>
       <c r="E51" t="s">
-        <v>826</v>
+        <v>812</v>
       </c>
       <c r="F51" t="str">
         <f t="shared" si="2"/>
@@ -4883,33 +4893,11 @@
       <c r="A52" t="s">
         <v>104</v>
       </c>
-      <c r="B52" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="C52" s="2" t="str">
-        <f>IFERROR(
-  INDEX(Sheet1!$B$1:$N$1,
-    MATCH(B52,
-      INDEX(Sheet1!$B$2:$N$170,
-        MATCH($A52,Sheet1!$A$2:$A$170,0),
-        0
-      ),
-      0
-    )
-  ),
-  ""
-)</f>
-        <v>1</v>
-      </c>
-      <c r="D52" t="s">
-        <v>677</v>
-      </c>
-      <c r="E52" t="s">
-        <v>789</v>
-      </c>
+      <c r="B52" s="2"/>
+      <c r="C52" s="2"/>
       <c r="F52" t="str">
         <f t="shared" si="2"/>
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="J52">
         <f t="shared" si="3"/>
@@ -4920,33 +4908,11 @@
       <c r="A53" t="s">
         <v>105</v>
       </c>
-      <c r="B53" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="C53" s="2" t="str">
-        <f>IFERROR(
-  INDEX(Sheet1!$B$1:$N$1,
-    MATCH(B53,
-      INDEX(Sheet1!$B$2:$N$170,
-        MATCH($A53,Sheet1!$A$2:$A$170,0),
-        0
-      ),
-      0
-    )
-  ),
-  ""
-)</f>
-        <v>1</v>
-      </c>
-      <c r="D53" t="s">
-        <v>677</v>
-      </c>
-      <c r="E53" t="s">
-        <v>790</v>
-      </c>
+      <c r="B53" s="2"/>
+      <c r="C53" s="2"/>
       <c r="F53" t="str">
         <f t="shared" si="2"/>
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="J53">
         <f t="shared" si="3"/>
@@ -4977,7 +4943,7 @@
         <v>770</v>
       </c>
       <c r="E54" t="s">
-        <v>827</v>
+        <v>813</v>
       </c>
       <c r="F54" t="str">
         <f t="shared" si="2"/>
@@ -4992,33 +4958,11 @@
       <c r="A55" t="s">
         <v>107</v>
       </c>
-      <c r="B55" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="C55" s="2" t="str">
-        <f>IFERROR(
-  INDEX(Sheet1!$B$1:$N$1,
-    MATCH(B55,
-      INDEX(Sheet1!$B$2:$N$170,
-        MATCH($A55,Sheet1!$A$2:$A$170,0),
-        0
-      ),
-      0
-    )
-  ),
-  ""
-)</f>
-        <v>1</v>
-      </c>
-      <c r="D55" t="s">
-        <v>677</v>
-      </c>
-      <c r="E55" t="s">
-        <v>791</v>
-      </c>
+      <c r="B55" s="2"/>
+      <c r="C55" s="2"/>
       <c r="F55" t="str">
         <f t="shared" si="2"/>
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="J55">
         <f t="shared" si="3"/>
@@ -5051,7 +4995,7 @@
         <v>677</v>
       </c>
       <c r="E56" t="s">
-        <v>792</v>
+        <v>788</v>
       </c>
       <c r="F56" t="str">
         <f t="shared" si="2"/>
@@ -5088,7 +5032,7 @@
         <v>677</v>
       </c>
       <c r="E57" t="s">
-        <v>793</v>
+        <v>789</v>
       </c>
       <c r="F57" t="str">
         <f t="shared" si="2"/>
@@ -5119,9 +5063,15 @@
 )</f>
         <v/>
       </c>
+      <c r="D58" t="s">
+        <v>9</v>
+      </c>
+      <c r="E58" t="s">
+        <v>823</v>
+      </c>
       <c r="F58" t="str">
         <f t="shared" si="2"/>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="J58">
         <f t="shared" si="3"/>
@@ -5154,7 +5104,7 @@
         <v>677</v>
       </c>
       <c r="E59" t="s">
-        <v>794</v>
+        <v>790</v>
       </c>
       <c r="F59" t="str">
         <f t="shared" si="2"/>
@@ -5338,7 +5288,7 @@
         <v>No</v>
       </c>
       <c r="G64" t="s">
-        <v>795</v>
+        <v>791</v>
       </c>
       <c r="J64">
         <f t="shared" si="3"/>
@@ -6325,7 +6275,7 @@
         <v>770</v>
       </c>
       <c r="E90" t="s">
-        <v>832</v>
+        <v>818</v>
       </c>
       <c r="F90" t="str">
         <f t="shared" si="4"/>
@@ -6362,7 +6312,7 @@
         <v>770</v>
       </c>
       <c r="E91" t="s">
-        <v>835</v>
+        <v>821</v>
       </c>
       <c r="F91" t="str">
         <f t="shared" si="4"/>
@@ -6399,7 +6349,7 @@
         <v>770</v>
       </c>
       <c r="E92" t="s">
-        <v>836</v>
+        <v>822</v>
       </c>
       <c r="F92" t="str">
         <f t="shared" si="4"/>
@@ -6582,10 +6532,10 @@
         <v>9</v>
       </c>
       <c r="E97" t="s">
-        <v>804</v>
+        <v>836</v>
       </c>
       <c r="F97" t="str">
-        <f>IF(E98&lt;&gt;"","Yes","No")</f>
+        <f>IF(E97&lt;&gt;"","Yes","No")</f>
         <v>Yes</v>
       </c>
       <c r="J97">
@@ -6597,7 +6547,9 @@
       <c r="A98" t="s">
         <v>150</v>
       </c>
-      <c r="B98" s="2"/>
+      <c r="B98" s="2" t="s">
+        <v>320</v>
+      </c>
       <c r="C98" s="2" t="str">
         <f>IFERROR(
   INDEX(Sheet1!$B$1:$N$1,
@@ -6611,20 +6563,20 @@
   ),
   ""
 )</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="D98" t="s">
-        <v>9</v>
+        <v>677</v>
       </c>
       <c r="E98" t="s">
-        <v>805</v>
+        <v>834</v>
       </c>
       <c r="F98" t="str">
-        <f>IF(E99&lt;&gt;"","Yes","No")</f>
+        <f t="shared" ref="F98:F161" si="6">IF(E98&lt;&gt;"","Yes","No")</f>
         <v>Yes</v>
       </c>
       <c r="J98">
-        <f t="shared" ref="J98:J129" si="6">IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(A98,"GPIO",""),"号","")),"")</f>
+        <f t="shared" ref="J98:J129" si="7">IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(A98,"GPIO",""),"号","")),"")</f>
         <v>96</v>
       </c>
     </row>
@@ -6632,7 +6584,9 @@
       <c r="A99" t="s">
         <v>151</v>
       </c>
-      <c r="B99" s="2"/>
+      <c r="B99" s="2" t="s">
+        <v>326</v>
+      </c>
       <c r="C99" s="2" t="str">
         <f>IFERROR(
   INDEX(Sheet1!$B$1:$N$1,
@@ -6646,20 +6600,20 @@
   ),
   ""
 )</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="D99" t="s">
-        <v>9</v>
+        <v>677</v>
       </c>
       <c r="E99" t="s">
-        <v>806</v>
+        <v>833</v>
       </c>
       <c r="F99" t="str">
-        <f>IF(E100&lt;&gt;"","Yes","No")</f>
+        <f t="shared" si="6"/>
         <v>Yes</v>
       </c>
       <c r="J99">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>97</v>
       </c>
     </row>
@@ -6687,14 +6641,14 @@
         <v>9</v>
       </c>
       <c r="E100" t="s">
-        <v>807</v>
+        <v>799</v>
       </c>
       <c r="F100" t="str">
-        <f>IF(E100&lt;&gt;"","Yes","No")</f>
+        <f t="shared" si="6"/>
         <v>Yes</v>
       </c>
       <c r="J100">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>98</v>
       </c>
     </row>
@@ -6702,7 +6656,9 @@
       <c r="A101" t="s">
         <v>153</v>
       </c>
-      <c r="B101" s="2"/>
+      <c r="B101" s="2" t="s">
+        <v>337</v>
+      </c>
       <c r="C101" s="2" t="str">
         <f>IFERROR(
   INDEX(Sheet1!$B$1:$N$1,
@@ -6716,17 +6672,20 @@
   ),
   ""
 )</f>
-        <v/>
+        <v>5</v>
+      </c>
+      <c r="D101" t="s">
+        <v>832</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>796</v>
+        <v>825</v>
       </c>
       <c r="F101" t="str">
-        <f t="shared" ref="F101:F131" si="7">IF(E101&lt;&gt;"","Yes","No")</f>
-        <v>No</v>
+        <f t="shared" si="6"/>
+        <v>Yes</v>
       </c>
       <c r="J101">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>99</v>
       </c>
     </row>
@@ -6759,11 +6718,11 @@
         <v>779</v>
       </c>
       <c r="F102" t="str">
+        <f t="shared" si="6"/>
+        <v>Yes</v>
+      </c>
+      <c r="J102">
         <f t="shared" si="7"/>
-        <v>Yes</v>
-      </c>
-      <c r="J102">
-        <f t="shared" si="6"/>
         <v>100</v>
       </c>
     </row>
@@ -6796,11 +6755,11 @@
         <v>780</v>
       </c>
       <c r="F103" t="str">
+        <f t="shared" si="6"/>
+        <v>Yes</v>
+      </c>
+      <c r="J103">
         <f t="shared" si="7"/>
-        <v>Yes</v>
-      </c>
-      <c r="J103">
-        <f t="shared" si="6"/>
         <v>101</v>
       </c>
     </row>
@@ -6833,11 +6792,11 @@
         <v>781</v>
       </c>
       <c r="F104" t="str">
+        <f t="shared" si="6"/>
+        <v>Yes</v>
+      </c>
+      <c r="J104">
         <f t="shared" si="7"/>
-        <v>Yes</v>
-      </c>
-      <c r="J104">
-        <f t="shared" si="6"/>
         <v>102</v>
       </c>
     </row>
@@ -6870,11 +6829,11 @@
         <v>782</v>
       </c>
       <c r="F105" t="str">
+        <f t="shared" si="6"/>
+        <v>Yes</v>
+      </c>
+      <c r="J105">
         <f t="shared" si="7"/>
-        <v>Yes</v>
-      </c>
-      <c r="J105">
-        <f t="shared" si="6"/>
         <v>103</v>
       </c>
     </row>
@@ -6904,14 +6863,14 @@
         <v>770</v>
       </c>
       <c r="E106" t="s">
-        <v>833</v>
+        <v>819</v>
       </c>
       <c r="F106" t="str">
+        <f t="shared" si="6"/>
+        <v>Yes</v>
+      </c>
+      <c r="J106">
         <f t="shared" si="7"/>
-        <v>Yes</v>
-      </c>
-      <c r="J106">
-        <f t="shared" si="6"/>
         <v>104</v>
       </c>
     </row>
@@ -6941,14 +6900,14 @@
         <v>770</v>
       </c>
       <c r="E107" t="s">
-        <v>834</v>
+        <v>820</v>
       </c>
       <c r="F107" t="str">
+        <f t="shared" si="6"/>
+        <v>Yes</v>
+      </c>
+      <c r="J107">
         <f t="shared" si="7"/>
-        <v>Yes</v>
-      </c>
-      <c r="J107">
-        <f t="shared" si="6"/>
         <v>105</v>
       </c>
     </row>
@@ -6976,14 +6935,14 @@
         <v>770</v>
       </c>
       <c r="E108" t="s">
-        <v>832</v>
+        <v>818</v>
       </c>
       <c r="F108" t="str">
-        <f>IF(E109&lt;&gt;"","Yes","No")</f>
+        <f t="shared" si="6"/>
         <v>Yes</v>
       </c>
       <c r="J108">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>106</v>
       </c>
     </row>
@@ -7011,14 +6970,14 @@
         <v>9</v>
       </c>
       <c r="E109" t="s">
-        <v>820</v>
+        <v>824</v>
       </c>
       <c r="F109" t="str">
-        <f>IF(E110&lt;&gt;"","Yes","No")</f>
+        <f t="shared" si="6"/>
         <v>Yes</v>
       </c>
       <c r="J109">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>107</v>
       </c>
     </row>
@@ -7046,14 +7005,14 @@
         <v>9</v>
       </c>
       <c r="E110" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="F110" t="str">
-        <f>IF(E111&lt;&gt;"","Yes","No")</f>
+        <f t="shared" si="6"/>
         <v>Yes</v>
       </c>
       <c r="J110">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>108</v>
       </c>
     </row>
@@ -7077,18 +7036,15 @@
 )</f>
         <v/>
       </c>
-      <c r="D111" t="s">
-        <v>9</v>
-      </c>
       <c r="E111" t="s">
-        <v>821</v>
+        <v>831</v>
       </c>
       <c r="F111" t="str">
-        <f>IF(E112&lt;&gt;"","Yes","No")</f>
-        <v>No</v>
+        <f>IF(E111&lt;&gt;"","Yes","No")</f>
+        <v>Yes</v>
       </c>
       <c r="J111">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>109</v>
       </c>
     </row>
@@ -7112,12 +7068,18 @@
 )</f>
         <v/>
       </c>
+      <c r="D112" t="s">
+        <v>9</v>
+      </c>
+      <c r="E112" t="s">
+        <v>806</v>
+      </c>
       <c r="F112" t="str">
+        <f t="shared" si="6"/>
+        <v>Yes</v>
+      </c>
+      <c r="J112">
         <f t="shared" si="7"/>
-        <v>No</v>
-      </c>
-      <c r="J112">
-        <f t="shared" si="6"/>
         <v>110</v>
       </c>
     </row>
@@ -7148,14 +7110,14 @@
         <v>165</v>
       </c>
       <c r="F113" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>Yes</v>
       </c>
       <c r="G113" t="s">
         <v>773</v>
       </c>
       <c r="J113">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>111</v>
       </c>
     </row>
@@ -7186,14 +7148,14 @@
         <v>166</v>
       </c>
       <c r="F114" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>Yes</v>
       </c>
       <c r="G114" t="s">
         <v>773</v>
       </c>
       <c r="J114">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>112</v>
       </c>
     </row>
@@ -7224,14 +7186,14 @@
         <v>167</v>
       </c>
       <c r="F115" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>Yes</v>
       </c>
       <c r="G115" t="s">
         <v>773</v>
       </c>
       <c r="J115">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>113</v>
       </c>
     </row>
@@ -7262,14 +7224,14 @@
         <v>168</v>
       </c>
       <c r="F116" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>Yes</v>
       </c>
       <c r="G116" t="s">
         <v>773</v>
       </c>
       <c r="J116">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>114</v>
       </c>
     </row>
@@ -7300,14 +7262,14 @@
         <v>228</v>
       </c>
       <c r="F117" t="str">
-        <f>IF(E117&lt;&gt;"","Yes","No")</f>
+        <f t="shared" si="6"/>
         <v>Yes</v>
       </c>
       <c r="G117" t="s">
         <v>783</v>
       </c>
       <c r="J117">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>115</v>
       </c>
     </row>
@@ -7338,14 +7300,14 @@
         <v>229</v>
       </c>
       <c r="F118" t="str">
-        <f>IF(E118&lt;&gt;"","Yes","No")</f>
+        <f t="shared" si="6"/>
         <v>Yes</v>
       </c>
       <c r="G118" t="s">
         <v>783</v>
       </c>
       <c r="J118">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>116</v>
       </c>
     </row>
@@ -7376,14 +7338,14 @@
         <v>234</v>
       </c>
       <c r="F119" t="str">
-        <f>IF(E119&lt;&gt;"","Yes","No")</f>
+        <f t="shared" si="6"/>
         <v>Yes</v>
       </c>
       <c r="G119" t="s">
         <v>783</v>
       </c>
       <c r="J119">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>117</v>
       </c>
     </row>
@@ -7414,14 +7376,14 @@
         <v>235</v>
       </c>
       <c r="F120" t="str">
-        <f>IF(E120&lt;&gt;"","Yes","No")</f>
+        <f t="shared" si="6"/>
         <v>Yes</v>
       </c>
       <c r="G120" t="s">
         <v>783</v>
       </c>
       <c r="J120">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>118</v>
       </c>
     </row>
@@ -7446,11 +7408,11 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <f>IF(E121&lt;&gt;"","Yes","No")</f>
+        <f t="shared" si="6"/>
         <v>No</v>
       </c>
       <c r="J121">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>119</v>
       </c>
     </row>
@@ -7474,18 +7436,12 @@
 )</f>
         <v/>
       </c>
-      <c r="D122" t="s">
-        <v>9</v>
-      </c>
-      <c r="E122" t="s">
-        <v>784</v>
-      </c>
       <c r="F122" t="str">
+        <f t="shared" si="6"/>
+        <v>No</v>
+      </c>
+      <c r="J122">
         <f t="shared" si="7"/>
-        <v>Yes</v>
-      </c>
-      <c r="J122">
-        <f t="shared" si="6"/>
         <v>120</v>
       </c>
     </row>
@@ -7513,14 +7469,14 @@
         <v>9</v>
       </c>
       <c r="E123" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="F123" t="str">
+        <f t="shared" si="6"/>
+        <v>Yes</v>
+      </c>
+      <c r="J123">
         <f t="shared" si="7"/>
-        <v>Yes</v>
-      </c>
-      <c r="J123">
-        <f t="shared" si="6"/>
         <v>121</v>
       </c>
     </row>
@@ -7553,11 +7509,11 @@
         <v>239</v>
       </c>
       <c r="F124" t="str">
+        <f t="shared" si="6"/>
+        <v>Yes</v>
+      </c>
+      <c r="J124">
         <f t="shared" si="7"/>
-        <v>Yes</v>
-      </c>
-      <c r="J124">
-        <f t="shared" si="6"/>
         <v>122</v>
       </c>
     </row>
@@ -7590,11 +7546,11 @@
         <v>238</v>
       </c>
       <c r="F125" t="str">
+        <f t="shared" si="6"/>
+        <v>Yes</v>
+      </c>
+      <c r="J125">
         <f t="shared" si="7"/>
-        <v>Yes</v>
-      </c>
-      <c r="J125">
-        <f t="shared" si="6"/>
         <v>123</v>
       </c>
     </row>
@@ -7627,11 +7583,11 @@
         <v>240</v>
       </c>
       <c r="F126" t="str">
+        <f t="shared" si="6"/>
+        <v>Yes</v>
+      </c>
+      <c r="J126">
         <f t="shared" si="7"/>
-        <v>Yes</v>
-      </c>
-      <c r="J126">
-        <f t="shared" si="6"/>
         <v>124</v>
       </c>
     </row>
@@ -7655,12 +7611,18 @@
 )</f>
         <v/>
       </c>
+      <c r="D127" t="s">
+        <v>9</v>
+      </c>
+      <c r="E127" t="s">
+        <v>837</v>
+      </c>
       <c r="F127" t="str">
+        <f t="shared" si="6"/>
+        <v>Yes</v>
+      </c>
+      <c r="J127">
         <f t="shared" si="7"/>
-        <v>No</v>
-      </c>
-      <c r="J127">
-        <f t="shared" si="6"/>
         <v>125</v>
       </c>
     </row>
@@ -7690,17 +7652,17 @@
         <v>49</v>
       </c>
       <c r="E128" t="s">
-        <v>800</v>
+        <v>795</v>
       </c>
       <c r="F128" t="str">
+        <f t="shared" si="6"/>
+        <v>Yes</v>
+      </c>
+      <c r="G128" t="s">
+        <v>798</v>
+      </c>
+      <c r="J128">
         <f t="shared" si="7"/>
-        <v>Yes</v>
-      </c>
-      <c r="G128" t="s">
-        <v>803</v>
-      </c>
-      <c r="J128">
-        <f t="shared" si="6"/>
         <v>126</v>
       </c>
     </row>
@@ -7724,12 +7686,18 @@
 )</f>
         <v/>
       </c>
+      <c r="D129" t="s">
+        <v>9</v>
+      </c>
+      <c r="E129" t="s">
+        <v>835</v>
+      </c>
       <c r="F129" t="str">
+        <f t="shared" si="6"/>
+        <v>Yes</v>
+      </c>
+      <c r="J129">
         <f t="shared" si="7"/>
-        <v>No</v>
-      </c>
-      <c r="J129">
-        <f t="shared" si="6"/>
         <v>127</v>
       </c>
     </row>
@@ -7759,14 +7727,14 @@
         <v>49</v>
       </c>
       <c r="E130" t="s">
+        <v>793</v>
+      </c>
+      <c r="F130" t="str">
+        <f t="shared" si="6"/>
+        <v>Yes</v>
+      </c>
+      <c r="G130" t="s">
         <v>798</v>
-      </c>
-      <c r="F130" t="str">
-        <f t="shared" si="7"/>
-        <v>Yes</v>
-      </c>
-      <c r="G130" t="s">
-        <v>803</v>
       </c>
       <c r="J130">
         <f t="shared" ref="J130:J161" si="8">IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(A130,"GPIO",""),"号","")),"")</f>
@@ -7794,7 +7762,7 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>No</v>
       </c>
       <c r="J131">
@@ -7828,10 +7796,10 @@
         <v>49</v>
       </c>
       <c r="E132" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="F132" t="str">
-        <f t="shared" ref="F132:F163" si="9">IF(E132&lt;&gt;"","Yes","No")</f>
+        <f t="shared" si="6"/>
         <v>Yes</v>
       </c>
       <c r="J132">
@@ -7865,10 +7833,10 @@
         <v>49</v>
       </c>
       <c r="E133" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="F133" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>Yes</v>
       </c>
       <c r="J133">
@@ -7902,10 +7870,10 @@
         <v>49</v>
       </c>
       <c r="E134" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="F134" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>Yes</v>
       </c>
       <c r="J134">
@@ -7937,10 +7905,10 @@
         <v>770</v>
       </c>
       <c r="E135" t="s">
-        <v>828</v>
+        <v>814</v>
       </c>
       <c r="F135" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>Yes</v>
       </c>
       <c r="J135">
@@ -7974,14 +7942,14 @@
         <v>49</v>
       </c>
       <c r="E136" t="s">
-        <v>799</v>
+        <v>794</v>
       </c>
       <c r="F136" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>Yes</v>
       </c>
       <c r="G136" t="s">
-        <v>801</v>
+        <v>796</v>
       </c>
       <c r="J136">
         <f t="shared" si="8"/>
@@ -8017,7 +7985,7 @@
         <v>705</v>
       </c>
       <c r="F137" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>Yes</v>
       </c>
       <c r="G137" t="s">
@@ -8054,14 +8022,14 @@
         <v>49</v>
       </c>
       <c r="E138" t="s">
+        <v>792</v>
+      </c>
+      <c r="F138" t="str">
+        <f t="shared" si="6"/>
+        <v>Yes</v>
+      </c>
+      <c r="G138" t="s">
         <v>797</v>
-      </c>
-      <c r="F138" t="str">
-        <f t="shared" si="9"/>
-        <v>Yes</v>
-      </c>
-      <c r="G138" t="s">
-        <v>802</v>
       </c>
       <c r="J138">
         <f t="shared" si="8"/>
@@ -8094,10 +8062,10 @@
         <v>770</v>
       </c>
       <c r="E139" t="s">
-        <v>829</v>
+        <v>815</v>
       </c>
       <c r="F139" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>Yes</v>
       </c>
       <c r="J139">
@@ -8131,10 +8099,10 @@
         <v>770</v>
       </c>
       <c r="E140" t="s">
-        <v>830</v>
+        <v>816</v>
       </c>
       <c r="F140" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>Yes</v>
       </c>
       <c r="J140">
@@ -8163,10 +8131,10 @@
         <v/>
       </c>
       <c r="E141" t="s">
-        <v>808</v>
+        <v>800</v>
       </c>
       <c r="F141" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>Yes</v>
       </c>
       <c r="J141">
@@ -8194,12 +8162,9 @@
 )</f>
         <v/>
       </c>
-      <c r="E142" t="s">
-        <v>809</v>
-      </c>
       <c r="F142" t="str">
-        <f t="shared" si="9"/>
-        <v>Yes</v>
+        <f t="shared" si="6"/>
+        <v>No</v>
       </c>
       <c r="J142">
         <f t="shared" si="8"/>
@@ -8227,10 +8192,10 @@
         <v/>
       </c>
       <c r="E143" t="s">
-        <v>810</v>
+        <v>801</v>
       </c>
       <c r="F143" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>Yes</v>
       </c>
       <c r="J143">
@@ -8259,10 +8224,10 @@
         <v/>
       </c>
       <c r="E144" t="s">
-        <v>811</v>
+        <v>802</v>
       </c>
       <c r="F144" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>Yes</v>
       </c>
       <c r="J144">
@@ -8299,7 +8264,7 @@
         <v>719</v>
       </c>
       <c r="F145" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>Yes</v>
       </c>
       <c r="G145" t="s">
@@ -8339,7 +8304,7 @@
         <v>720</v>
       </c>
       <c r="F146" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>Yes</v>
       </c>
       <c r="G146" t="s">
@@ -8379,7 +8344,7 @@
         <v>532</v>
       </c>
       <c r="F147" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>Yes</v>
       </c>
       <c r="G147" t="s">
@@ -8419,7 +8384,7 @@
         <v>537</v>
       </c>
       <c r="F148" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>Yes</v>
       </c>
       <c r="G148" t="s">
@@ -8450,9 +8415,15 @@
 )</f>
         <v/>
       </c>
+      <c r="D149" t="s">
+        <v>826</v>
+      </c>
+      <c r="E149" t="s">
+        <v>828</v>
+      </c>
       <c r="F149" t="str">
-        <f t="shared" si="9"/>
-        <v>No</v>
+        <f t="shared" si="6"/>
+        <v>Yes</v>
       </c>
       <c r="J149">
         <f t="shared" si="8"/>
@@ -8488,7 +8459,7 @@
         <v>695</v>
       </c>
       <c r="F150" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>Yes</v>
       </c>
       <c r="G150" t="s">
@@ -8520,7 +8491,7 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>No</v>
       </c>
       <c r="J151">
@@ -8557,7 +8528,7 @@
         <v>446</v>
       </c>
       <c r="F152" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>Yes</v>
       </c>
       <c r="G152" t="s">
@@ -8597,7 +8568,7 @@
         <v>439</v>
       </c>
       <c r="F153" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>Yes</v>
       </c>
       <c r="G153" t="s">
@@ -8629,10 +8600,10 @@
         <v/>
       </c>
       <c r="E154" t="s">
-        <v>812</v>
+        <v>803</v>
       </c>
       <c r="F154" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>Yes</v>
       </c>
       <c r="J154">
@@ -8660,12 +8631,9 @@
 )</f>
         <v/>
       </c>
-      <c r="E155" t="s">
-        <v>813</v>
-      </c>
       <c r="F155" t="str">
-        <f t="shared" si="9"/>
-        <v>Yes</v>
+        <f t="shared" si="6"/>
+        <v>No</v>
       </c>
       <c r="J155">
         <f t="shared" si="8"/>
@@ -8693,10 +8661,10 @@
         <v/>
       </c>
       <c r="E156" t="s">
-        <v>814</v>
+        <v>804</v>
       </c>
       <c r="F156" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>Yes</v>
       </c>
       <c r="J156">
@@ -8725,10 +8693,10 @@
         <v/>
       </c>
       <c r="E157" t="s">
-        <v>815</v>
+        <v>805</v>
       </c>
       <c r="F157" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>Yes</v>
       </c>
       <c r="J157">
@@ -8765,7 +8733,7 @@
         <v>696</v>
       </c>
       <c r="F158" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>Yes</v>
       </c>
       <c r="G158" t="s">
@@ -8796,9 +8764,15 @@
 )</f>
         <v/>
       </c>
+      <c r="D159" t="s">
+        <v>826</v>
+      </c>
+      <c r="E159" t="s">
+        <v>827</v>
+      </c>
       <c r="F159" t="str">
-        <f t="shared" si="9"/>
-        <v>No</v>
+        <f t="shared" si="6"/>
+        <v>Yes</v>
       </c>
       <c r="J159">
         <f t="shared" si="8"/>
@@ -8826,7 +8800,7 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>No</v>
       </c>
       <c r="J160">
@@ -8863,7 +8837,7 @@
         <v>697</v>
       </c>
       <c r="F161" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="6"/>
         <v>Yes</v>
       </c>
       <c r="G161" t="s">
@@ -8903,7 +8877,7 @@
         <v>698</v>
       </c>
       <c r="F162" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="F162:F191" si="9">IF(E162&lt;&gt;"","Yes","No")</f>
         <v>Yes</v>
       </c>
       <c r="G162" t="s">
@@ -8974,12 +8948,9 @@
 )</f>
         <v/>
       </c>
-      <c r="E164" t="s">
-        <v>816</v>
-      </c>
       <c r="F164" t="str">
-        <f t="shared" ref="F164:F195" si="11">IF(E164&lt;&gt;"","Yes","No")</f>
-        <v>Yes</v>
+        <f t="shared" si="9"/>
+        <v>No</v>
       </c>
       <c r="J164">
         <f t="shared" si="10"/>
@@ -9006,12 +8977,9 @@
 )</f>
         <v/>
       </c>
-      <c r="E165" t="s">
-        <v>817</v>
-      </c>
       <c r="F165" t="str">
-        <f t="shared" si="11"/>
-        <v>Yes</v>
+        <f t="shared" si="9"/>
+        <v>No</v>
       </c>
       <c r="J165">
         <f t="shared" si="10"/>
@@ -9039,10 +9007,10 @@
         <v/>
       </c>
       <c r="E166" t="s">
-        <v>819</v>
+        <v>808</v>
       </c>
       <c r="F166" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>Yes</v>
       </c>
       <c r="J166">
@@ -9071,10 +9039,10 @@
         <v/>
       </c>
       <c r="E167" t="s">
-        <v>818</v>
+        <v>807</v>
       </c>
       <c r="F167" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>Yes</v>
       </c>
       <c r="J167">
@@ -9106,10 +9074,10 @@
         <v>9</v>
       </c>
       <c r="E168" t="s">
-        <v>822</v>
+        <v>810</v>
       </c>
       <c r="F168" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>Yes</v>
       </c>
       <c r="J168">
@@ -9141,10 +9109,10 @@
         <v>9</v>
       </c>
       <c r="E169" t="s">
-        <v>823</v>
+        <v>817</v>
       </c>
       <c r="F169" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="9"/>
         <v>Yes</v>
       </c>
       <c r="J169">
@@ -9176,10 +9144,10 @@
         <v>9</v>
       </c>
       <c r="E170" t="s">
-        <v>824</v>
+        <v>809</v>
       </c>
       <c r="F170" t="str">
-        <f t="shared" si="11"/>
+        <f>IF(E170&lt;&gt;"","Yes","No")</f>
         <v>Yes</v>
       </c>
       <c r="J170">
@@ -9195,7 +9163,7 @@
         <v>17</v>
       </c>
       <c r="F171" t="str">
-        <f t="shared" ref="F171:F191" si="12">IF(E171&lt;&gt;"","Yes","No")</f>
+        <f t="shared" si="9"/>
         <v>No</v>
       </c>
       <c r="J171" t="str">
@@ -9211,7 +9179,7 @@
         <v>17</v>
       </c>
       <c r="F172" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>No</v>
       </c>
     </row>
@@ -9223,7 +9191,7 @@
         <v>17</v>
       </c>
       <c r="F173" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>No</v>
       </c>
     </row>
@@ -9235,7 +9203,7 @@
         <v>17</v>
       </c>
       <c r="F174" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>No</v>
       </c>
     </row>
@@ -9247,7 +9215,7 @@
         <v>17</v>
       </c>
       <c r="F175" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>No</v>
       </c>
     </row>
@@ -9259,7 +9227,7 @@
         <v>17</v>
       </c>
       <c r="F176" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>No</v>
       </c>
     </row>
@@ -9271,7 +9239,7 @@
         <v>17</v>
       </c>
       <c r="F177" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>No</v>
       </c>
     </row>
@@ -9283,7 +9251,7 @@
         <v>17</v>
       </c>
       <c r="F178" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>No</v>
       </c>
     </row>
@@ -9295,7 +9263,7 @@
         <v>17</v>
       </c>
       <c r="F179" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>No</v>
       </c>
     </row>
@@ -9307,7 +9275,7 @@
         <v>17</v>
       </c>
       <c r="F180" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>No</v>
       </c>
     </row>
@@ -9319,7 +9287,7 @@
         <v>17</v>
       </c>
       <c r="F181" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>No</v>
       </c>
     </row>
@@ -9331,7 +9299,7 @@
         <v>17</v>
       </c>
       <c r="F182" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>No</v>
       </c>
     </row>
@@ -9343,7 +9311,7 @@
         <v>17</v>
       </c>
       <c r="F183" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>No</v>
       </c>
     </row>
@@ -9355,7 +9323,7 @@
         <v>17</v>
       </c>
       <c r="F184" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>No</v>
       </c>
     </row>
@@ -9367,7 +9335,7 @@
         <v>17</v>
       </c>
       <c r="F185" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>No</v>
       </c>
     </row>
@@ -9379,7 +9347,7 @@
         <v>17</v>
       </c>
       <c r="F186" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>No</v>
       </c>
     </row>
@@ -9391,7 +9359,7 @@
         <v>17</v>
       </c>
       <c r="F187" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>No</v>
       </c>
     </row>
@@ -9403,7 +9371,7 @@
         <v>17</v>
       </c>
       <c r="F188" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>No</v>
       </c>
     </row>
@@ -9415,7 +9383,7 @@
         <v>17</v>
       </c>
       <c r="F189" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>No</v>
       </c>
     </row>
@@ -9427,7 +9395,7 @@
         <v>17</v>
       </c>
       <c r="F190" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>No</v>
       </c>
     </row>
@@ -9439,7 +9407,7 @@
         <v>17</v>
       </c>
       <c r="F191" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="9"/>
         <v>No</v>
       </c>
     </row>
@@ -9454,17 +9422,17 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C2F6B898-CAC9-477D-92FC-DAF87F5E1AD8}">
-          <x14:formula1>
-            <xm:f>Lists!$A$2:$A$17</xm:f>
-          </x14:formula1>
-          <xm:sqref>D1:D1048576</xm:sqref>
-        </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{2288AA12-4D70-42A0-9B9E-3883A36A8741}">
           <x14:formula1>
             <xm:f>OFFSET(Sheet1!$B$1, MATCH(A2, Sheet1!$A$2:$A$170, 0), 0, 1, 13)</xm:f>
           </x14:formula1>
           <xm:sqref>B2:B170</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C2F6B898-CAC9-477D-92FC-DAF87F5E1AD8}">
+          <x14:formula1>
+            <xm:f>Lists!$A$2:$A$17</xm:f>
+          </x14:formula1>
+          <xm:sqref>D1:D110 D203:D1048576 D112:D201</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/28388motherboard/TMS320F28388D_PinMap.xlsx
+++ b/28388motherboard/TMS320F28388D_PinMap.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\codefile\28388Board\mmlab-12PhaseDrive-388Slave\28388motherboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88B481A3-96C1-479A-9AB9-F8316AAF13E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A5699F5-47FA-4E7A-B7DE-99E0E47383BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="26010" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38400" yWindow="3900" windowWidth="38700" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PinMap" sheetId="1" r:id="rId1"/>
@@ -18,14 +18,14 @@
     <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">PinMap!$A$1:$J$170</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">PinMap!$A$1:$J$191</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1905" uniqueCount="836">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1907" uniqueCount="837">
   <si>
     <t>Comment（备注）</t>
   </si>
@@ -2508,15 +2508,133 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>DSP_Discharge4_EN</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DSP_PWM1_~{FAULT}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DSP_PWM4_~{FAULT}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DSP_Temperature2</t>
+  </si>
+  <si>
+    <t>DSP_Temperature4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HALL1_UY</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HALL1_WY</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MCU_485D_1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MCU_485R_1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>485_RTS_1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>485_RTS_2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MCU_485D_2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MCU_485R_2</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HALL1_VY</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>485_RTS_4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MCU_485D_4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MCU_485R_4</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MCU_485D_3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MCU_485R_3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DSP_Temperature1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DSP_Discharge2_EN</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MQEP1Z</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hall</t>
+  </si>
+  <si>
+    <t>HALL2_U</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HALL2_V</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>HALL2_W</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DSP_PWM2~{_ENABLE}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DSP_PWM2_~{FAULT}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>eQEP</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MQEP1B</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>MQEP1A</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>DSP_Discharge3_EN</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>DSP_Discharge4_EN</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>DSP_PWM1_~{FAULT}</t>
+    <t>DSP_PWM3~{_ENABLE}</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -2524,137 +2642,23 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>DSP_PWM4_~{FAULT}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>DSP_Temperature2</t>
-  </si>
-  <si>
-    <t>DSP_Temperature4</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>HALL1_UY</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>HALL1_WY</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>MCU_485D_1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>MCU_485R_1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>485_RTS_1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>485_RTS_2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>MCU_485D_2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>MCU_485R_2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>HALL1_VY</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>485_RTS_4</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>MCU_485D_4</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>MCU_485R_4</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>MCU_485D_3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>MCU_485R_3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>DSP_Temperature1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>DSP_Discharge2_EN</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>MQEP1Z</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Hall</t>
-  </si>
-  <si>
-    <t>HALL2_U</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>HALL2_V</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>HALL2_W</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>DSP_PWM2~{_ENABLE}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>DSP_PWM2_~{FAULT}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>eQEP</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>MQEP1B</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>MQEP1A</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>DSP_Discharge3_EN</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>DSP_PWM3~{_ENABLE}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>DSP_PWM3_~{FAULT}</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>DSP_Temperature3</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>DSP_PWM4~{_ENABLE}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DI-1-DSP-3.3V</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>DSP_PWM1~{_ENABLE}</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GPIO154</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -3022,20 +3026,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:J191"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="10.90625" customWidth="1"/>
-    <col min="2" max="2" width="20.7265625" customWidth="1"/>
-    <col min="3" max="3" width="19.6328125" customWidth="1"/>
-    <col min="4" max="4" width="13.6328125" customWidth="1"/>
-    <col min="5" max="5" width="24.6328125" customWidth="1"/>
+    <col min="1" max="1" width="10.875" customWidth="1"/>
+    <col min="2" max="2" width="20.75" customWidth="1"/>
+    <col min="3" max="3" width="19.625" customWidth="1"/>
+    <col min="4" max="4" width="13.625" customWidth="1"/>
+    <col min="5" max="5" width="24.625" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
-    <col min="7" max="7" width="18.08984375" customWidth="1"/>
-    <col min="8" max="8" width="9.36328125" customWidth="1"/>
+    <col min="7" max="7" width="18.125" customWidth="1"/>
+    <col min="8" max="8" width="9.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>42</v>
       </c>
@@ -3067,7 +3072,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>223</v>
       </c>
@@ -3104,7 +3109,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>224</v>
       </c>
@@ -3141,7 +3146,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
         <v>56</v>
       </c>
@@ -3178,7 +3183,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
         <v>57</v>
       </c>
@@ -3215,7 +3220,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
         <v>58</v>
       </c>
@@ -3252,7 +3257,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
         <v>59</v>
       </c>
@@ -3289,7 +3294,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
         <v>60</v>
       </c>
@@ -3326,7 +3331,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
         <v>61</v>
       </c>
@@ -3363,7 +3368,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
         <v>62</v>
       </c>
@@ -3400,7 +3405,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
         <v>63</v>
       </c>
@@ -3437,7 +3442,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A12" t="s">
         <v>64</v>
       </c>
@@ -3474,7 +3479,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A13" t="s">
         <v>65</v>
       </c>
@@ -3511,7 +3516,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A14" t="s">
         <v>66</v>
       </c>
@@ -3548,7 +3553,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A15" t="s">
         <v>67</v>
       </c>
@@ -3585,7 +3590,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A16" t="s">
         <v>68</v>
       </c>
@@ -3622,7 +3627,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A17" t="s">
         <v>69</v>
       </c>
@@ -3659,7 +3664,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A18" t="s">
         <v>70</v>
       </c>
@@ -3696,7 +3701,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A19" t="s">
         <v>71</v>
       </c>
@@ -3733,7 +3738,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A20" t="s">
         <v>72</v>
       </c>
@@ -3770,7 +3775,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A21" t="s">
         <v>73</v>
       </c>
@@ -3807,7 +3812,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A22" t="s">
         <v>74</v>
       </c>
@@ -3844,7 +3849,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A23" t="s">
         <v>75</v>
       </c>
@@ -3881,7 +3886,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A24" t="s">
         <v>76</v>
       </c>
@@ -3918,7 +3923,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A25" t="s">
         <v>77</v>
       </c>
@@ -3955,7 +3960,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A26" t="s">
         <v>78</v>
       </c>
@@ -3992,7 +3997,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A27" t="s">
         <v>79</v>
       </c>
@@ -4029,7 +4034,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A28" t="s">
         <v>80</v>
       </c>
@@ -4066,7 +4071,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A29" t="s">
         <v>81</v>
       </c>
@@ -4103,7 +4108,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A30" t="s">
         <v>82</v>
       </c>
@@ -4127,7 +4132,7 @@
         <v>9</v>
       </c>
       <c r="E30" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="F30" t="str">
         <f t="shared" si="0"/>
@@ -4138,7 +4143,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A31" t="s">
         <v>83</v>
       </c>
@@ -4173,7 +4178,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A32" t="s">
         <v>84</v>
       </c>
@@ -4210,7 +4215,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A33" t="s">
         <v>85</v>
       </c>
@@ -4247,7 +4252,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A34" t="s">
         <v>86</v>
       </c>
@@ -4284,7 +4289,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A35" t="s">
         <v>87</v>
       </c>
@@ -4321,7 +4326,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A36" t="s">
         <v>88</v>
       </c>
@@ -4358,7 +4363,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A37" t="s">
         <v>89</v>
       </c>
@@ -4395,7 +4400,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A38" t="s">
         <v>90</v>
       </c>
@@ -4410,7 +4415,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A39" t="s">
         <v>91</v>
       </c>
@@ -4445,7 +4450,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A40" t="s">
         <v>92</v>
       </c>
@@ -4482,7 +4487,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A41" t="s">
         <v>93</v>
       </c>
@@ -4519,7 +4524,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A42" t="s">
         <v>94</v>
       </c>
@@ -4543,7 +4548,7 @@
         <v>9</v>
       </c>
       <c r="E42" t="s">
-        <v>826</v>
+        <v>835</v>
       </c>
       <c r="F42" t="str">
         <f t="shared" si="2"/>
@@ -4554,7 +4559,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A43" t="s">
         <v>95</v>
       </c>
@@ -4589,7 +4594,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A44" t="s">
         <v>96</v>
       </c>
@@ -4610,10 +4615,10 @@
         <v/>
       </c>
       <c r="D44" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="E44" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="F44" t="str">
         <f t="shared" si="2"/>
@@ -4624,7 +4629,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A45" t="s">
         <v>97</v>
       </c>
@@ -4653,7 +4658,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A46" t="s">
         <v>98</v>
       </c>
@@ -4693,7 +4698,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A47" t="s">
         <v>99</v>
       </c>
@@ -4733,7 +4738,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A48" t="s">
         <v>100</v>
       </c>
@@ -4773,7 +4778,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A49" t="s">
         <v>101</v>
       </c>
@@ -4813,7 +4818,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A50" t="s">
         <v>102</v>
       </c>
@@ -4839,7 +4844,7 @@
         <v>768</v>
       </c>
       <c r="E50" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="F50" t="str">
         <f t="shared" si="2"/>
@@ -4850,7 +4855,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A51" t="s">
         <v>103</v>
       </c>
@@ -4876,7 +4881,7 @@
         <v>768</v>
       </c>
       <c r="E51" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="F51" t="str">
         <f t="shared" si="2"/>
@@ -4887,7 +4892,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A52" t="s">
         <v>104</v>
       </c>
@@ -4902,7 +4907,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A53" t="s">
         <v>105</v>
       </c>
@@ -4917,7 +4922,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A54" t="s">
         <v>106</v>
       </c>
@@ -4941,7 +4946,7 @@
         <v>768</v>
       </c>
       <c r="E54" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="F54" t="str">
         <f t="shared" si="2"/>
@@ -4952,7 +4957,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A55" t="s">
         <v>107</v>
       </c>
@@ -4967,7 +4972,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A56" t="s">
         <v>108</v>
       </c>
@@ -5004,7 +5009,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A57" t="s">
         <v>109</v>
       </c>
@@ -5041,7 +5046,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A58" t="s">
         <v>110</v>
       </c>
@@ -5065,7 +5070,7 @@
         <v>9</v>
       </c>
       <c r="E58" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="F58" t="str">
         <f t="shared" si="2"/>
@@ -5076,7 +5081,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A59" t="s">
         <v>111</v>
       </c>
@@ -5113,7 +5118,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A60" t="s">
         <v>112</v>
       </c>
@@ -5150,7 +5155,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A61" t="s">
         <v>113</v>
       </c>
@@ -5187,7 +5192,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A62" t="s">
         <v>114</v>
       </c>
@@ -5224,7 +5229,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A63" t="s">
         <v>115</v>
       </c>
@@ -5261,7 +5266,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A64" t="s">
         <v>116</v>
       </c>
@@ -5293,7 +5298,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A65" t="s">
         <v>117</v>
       </c>
@@ -5333,7 +5338,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A66" t="s">
         <v>118</v>
       </c>
@@ -5362,7 +5367,7 @@
         <v>710</v>
       </c>
       <c r="F66" t="str">
-        <f t="shared" ref="F66:F96" si="4">IF(E66&lt;&gt;"","Yes","No")</f>
+        <f t="shared" ref="F66:F97" si="4">IF(E66&lt;&gt;"","Yes","No")</f>
         <v>Yes</v>
       </c>
       <c r="G66" t="s">
@@ -5373,7 +5378,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="67" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A67" t="s">
         <v>119</v>
       </c>
@@ -5413,7 +5418,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="68" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A68" t="s">
         <v>120</v>
       </c>
@@ -5453,7 +5458,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="69" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A69" t="s">
         <v>121</v>
       </c>
@@ -5482,7 +5487,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="70" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A70" t="s">
         <v>122</v>
       </c>
@@ -5522,7 +5527,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A71" t="s">
         <v>123</v>
       </c>
@@ -5562,7 +5567,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A72" t="s">
         <v>124</v>
       </c>
@@ -5602,7 +5607,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A73" t="s">
         <v>125</v>
       </c>
@@ -5642,7 +5647,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A74" t="s">
         <v>126</v>
       </c>
@@ -5671,7 +5676,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A75" t="s">
         <v>127</v>
       </c>
@@ -5711,7 +5716,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="76" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A76" t="s">
         <v>128</v>
       </c>
@@ -5751,7 +5756,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="77" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A77" t="s">
         <v>129</v>
       </c>
@@ -5791,7 +5796,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="78" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A78" t="s">
         <v>130</v>
       </c>
@@ -5831,7 +5836,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="79" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A79" t="s">
         <v>131</v>
       </c>
@@ -5871,7 +5876,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="80" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A80" t="s">
         <v>132</v>
       </c>
@@ -5911,7 +5916,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="81" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A81" t="s">
         <v>133</v>
       </c>
@@ -5951,7 +5956,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="82" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A82" t="s">
         <v>134</v>
       </c>
@@ -5991,7 +5996,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="83" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A83" t="s">
         <v>135</v>
       </c>
@@ -6031,7 +6036,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="84" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A84" t="s">
         <v>136</v>
       </c>
@@ -6071,7 +6076,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="85" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A85" t="s">
         <v>137</v>
       </c>
@@ -6111,7 +6116,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="86" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A86" t="s">
         <v>138</v>
       </c>
@@ -6140,7 +6145,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="87" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A87" t="s">
         <v>139</v>
       </c>
@@ -6180,7 +6185,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="88" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A88" t="s">
         <v>140</v>
       </c>
@@ -6209,7 +6214,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="89" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A89" t="s">
         <v>141</v>
       </c>
@@ -6249,7 +6254,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="90" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A90" t="s">
         <v>142</v>
       </c>
@@ -6273,7 +6278,7 @@
         <v>768</v>
       </c>
       <c r="E90" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="F90" t="str">
         <f t="shared" si="4"/>
@@ -6284,7 +6289,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="91" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A91" t="s">
         <v>143</v>
       </c>
@@ -6310,7 +6315,7 @@
         <v>768</v>
       </c>
       <c r="E91" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="F91" t="str">
         <f t="shared" si="4"/>
@@ -6321,7 +6326,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="92" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A92" t="s">
         <v>144</v>
       </c>
@@ -6347,7 +6352,7 @@
         <v>768</v>
       </c>
       <c r="E92" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="F92" t="str">
         <f t="shared" si="4"/>
@@ -6358,7 +6363,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="93" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A93" t="s">
         <v>145</v>
       </c>
@@ -6395,7 +6400,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="94" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A94" t="s">
         <v>146</v>
       </c>
@@ -6432,7 +6437,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="95" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A95" t="s">
         <v>147</v>
       </c>
@@ -6469,7 +6474,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="96" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A96" t="s">
         <v>148</v>
       </c>
@@ -6506,7 +6511,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A97" t="s">
         <v>149</v>
       </c>
@@ -6530,10 +6535,10 @@
         <v>9</v>
       </c>
       <c r="E97" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="F97" t="str">
-        <f>IF(E97&lt;&gt;"","Yes","No")</f>
+        <f t="shared" si="4"/>
         <v>Yes</v>
       </c>
       <c r="J97">
@@ -6541,7 +6546,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A98" t="s">
         <v>150</v>
       </c>
@@ -6567,10 +6572,10 @@
         <v>675</v>
       </c>
       <c r="E98" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="F98" t="str">
-        <f t="shared" ref="F98:F161" si="6">IF(E98&lt;&gt;"","Yes","No")</f>
+        <f t="shared" ref="F98:F129" si="6">IF(E98&lt;&gt;"","Yes","No")</f>
         <v>Yes</v>
       </c>
       <c r="J98">
@@ -6578,7 +6583,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A99" t="s">
         <v>151</v>
       </c>
@@ -6604,7 +6609,7 @@
         <v>675</v>
       </c>
       <c r="E99" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="F99" t="str">
         <f t="shared" si="6"/>
@@ -6615,7 +6620,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A100" t="s">
         <v>152</v>
       </c>
@@ -6644,7 +6649,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A101" t="s">
         <v>153</v>
       </c>
@@ -6667,10 +6672,10 @@
         <v>5</v>
       </c>
       <c r="D101" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="F101" t="str">
         <f t="shared" si="6"/>
@@ -6681,7 +6686,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A102" t="s">
         <v>154</v>
       </c>
@@ -6718,7 +6723,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A103" t="s">
         <v>155</v>
       </c>
@@ -6755,7 +6760,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A104" t="s">
         <v>156</v>
       </c>
@@ -6792,7 +6797,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A105" t="s">
         <v>157</v>
       </c>
@@ -6829,7 +6834,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A106" t="s">
         <v>158</v>
       </c>
@@ -6855,7 +6860,7 @@
         <v>768</v>
       </c>
       <c r="E106" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="F106" t="str">
         <f t="shared" si="6"/>
@@ -6866,7 +6871,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A107" t="s">
         <v>159</v>
       </c>
@@ -6892,7 +6897,7 @@
         <v>768</v>
       </c>
       <c r="E107" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="F107" t="str">
         <f t="shared" si="6"/>
@@ -6903,7 +6908,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A108" t="s">
         <v>160</v>
       </c>
@@ -6927,7 +6932,7 @@
         <v>768</v>
       </c>
       <c r="E108" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="F108" t="str">
         <f t="shared" si="6"/>
@@ -6938,7 +6943,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A109" t="s">
         <v>161</v>
       </c>
@@ -6962,7 +6967,7 @@
         <v>9</v>
       </c>
       <c r="E109" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="F109" t="str">
         <f t="shared" si="6"/>
@@ -6973,7 +6978,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A110" t="s">
         <v>162</v>
       </c>
@@ -6997,7 +7002,7 @@
         <v>9</v>
       </c>
       <c r="E110" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="F110" t="str">
         <f t="shared" si="6"/>
@@ -7008,7 +7013,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A111" t="s">
         <v>163</v>
       </c>
@@ -7032,10 +7037,10 @@
         <v>9</v>
       </c>
       <c r="E111" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="F111" t="str">
-        <f>IF(E111&lt;&gt;"","Yes","No")</f>
+        <f t="shared" si="6"/>
         <v>Yes</v>
       </c>
       <c r="J111">
@@ -7043,7 +7048,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A112" t="s">
         <v>164</v>
       </c>
@@ -7067,7 +7072,7 @@
         <v>9</v>
       </c>
       <c r="E112" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="F112" t="str">
         <f t="shared" si="6"/>
@@ -7078,7 +7083,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="113" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A113" t="s">
         <v>165</v>
       </c>
@@ -7116,7 +7121,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="114" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A114" t="s">
         <v>166</v>
       </c>
@@ -7154,7 +7159,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="115" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A115" t="s">
         <v>167</v>
       </c>
@@ -7192,7 +7197,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="116" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A116" t="s">
         <v>168</v>
       </c>
@@ -7230,7 +7235,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="117" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A117" t="s">
         <v>169</v>
       </c>
@@ -7268,7 +7273,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="118" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A118" t="s">
         <v>170</v>
       </c>
@@ -7306,7 +7311,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="119" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A119" t="s">
         <v>171</v>
       </c>
@@ -7330,7 +7335,7 @@
         <v>9</v>
       </c>
       <c r="E119" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="F119" t="str">
         <f t="shared" si="6"/>
@@ -7341,7 +7346,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="120" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A120" t="s">
         <v>172</v>
       </c>
@@ -7365,7 +7370,7 @@
         <v>9</v>
       </c>
       <c r="E120" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="F120" t="str">
         <f t="shared" si="6"/>
@@ -7376,7 +7381,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="121" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A121" t="s">
         <v>173</v>
       </c>
@@ -7405,7 +7410,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="122" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A122" t="s">
         <v>174</v>
       </c>
@@ -7425,16 +7430,22 @@
 )</f>
         <v/>
       </c>
+      <c r="D122" t="s">
+        <v>9</v>
+      </c>
+      <c r="E122" t="s">
+        <v>834</v>
+      </c>
       <c r="F122" t="str">
         <f t="shared" si="6"/>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="J122">
         <f t="shared" si="7"/>
         <v>120</v>
       </c>
     </row>
-    <row r="123" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A123" t="s">
         <v>175</v>
       </c>
@@ -7458,7 +7469,7 @@
         <v>9</v>
       </c>
       <c r="E123" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="F123" t="str">
         <f t="shared" si="6"/>
@@ -7469,7 +7480,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="124" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A124" t="s">
         <v>176</v>
       </c>
@@ -7506,7 +7517,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="125" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A125" t="s">
         <v>177</v>
       </c>
@@ -7543,7 +7554,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="126" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A126" t="s">
         <v>178</v>
       </c>
@@ -7580,7 +7591,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="127" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A127" t="s">
         <v>179</v>
       </c>
@@ -7604,7 +7615,7 @@
         <v>9</v>
       </c>
       <c r="E127" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="F127" t="str">
         <f t="shared" si="6"/>
@@ -7615,7 +7626,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="128" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A128" t="s">
         <v>180</v>
       </c>
@@ -7655,7 +7666,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A129" t="s">
         <v>181</v>
       </c>
@@ -7679,7 +7690,7 @@
         <v>9</v>
       </c>
       <c r="E129" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="F129" t="str">
         <f t="shared" si="6"/>
@@ -7690,7 +7701,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A130" t="s">
         <v>182</v>
       </c>
@@ -7719,18 +7730,18 @@
         <v>791</v>
       </c>
       <c r="F130" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="F130:F161" si="8">IF(E130&lt;&gt;"","Yes","No")</f>
         <v>Yes</v>
       </c>
       <c r="G130" t="s">
         <v>796</v>
       </c>
       <c r="J130">
-        <f t="shared" ref="J130:J161" si="8">IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(A130,"GPIO",""),"号","")),"")</f>
+        <f t="shared" ref="J130:J142" si="9">IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(A130,"GPIO",""),"号","")),"")</f>
         <v>128</v>
       </c>
     </row>
-    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A131" t="s">
         <v>183</v>
       </c>
@@ -7754,18 +7765,18 @@
         <v>9</v>
       </c>
       <c r="E131" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="F131" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Yes</v>
       </c>
       <c r="J131">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>129</v>
       </c>
     </row>
-    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A132" t="s">
         <v>184</v>
       </c>
@@ -7794,15 +7805,15 @@
         <v>783</v>
       </c>
       <c r="F132" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Yes</v>
       </c>
       <c r="J132">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>130</v>
       </c>
     </row>
-    <row r="133" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A133" t="s">
         <v>185</v>
       </c>
@@ -7831,15 +7842,15 @@
         <v>785</v>
       </c>
       <c r="F133" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Yes</v>
       </c>
       <c r="J133">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>131</v>
       </c>
     </row>
-    <row r="134" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A134" t="s">
         <v>186</v>
       </c>
@@ -7868,15 +7879,15 @@
         <v>784</v>
       </c>
       <c r="F134" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Yes</v>
       </c>
       <c r="J134">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>132</v>
       </c>
     </row>
-    <row r="135" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A135" t="s">
         <v>187</v>
       </c>
@@ -7900,18 +7911,18 @@
         <v>768</v>
       </c>
       <c r="E135" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="F135" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Yes</v>
       </c>
       <c r="J135">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>133</v>
       </c>
     </row>
-    <row r="136" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A136" t="s">
         <v>188</v>
       </c>
@@ -7940,18 +7951,18 @@
         <v>792</v>
       </c>
       <c r="F136" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Yes</v>
       </c>
       <c r="G136" t="s">
         <v>794</v>
       </c>
       <c r="J136">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>134</v>
       </c>
     </row>
-    <row r="137" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A137" t="s">
         <v>189</v>
       </c>
@@ -7980,18 +7991,18 @@
         <v>703</v>
       </c>
       <c r="F137" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Yes</v>
       </c>
       <c r="G137" t="s">
         <v>770</v>
       </c>
       <c r="J137">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>135</v>
       </c>
     </row>
-    <row r="138" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A138" t="s">
         <v>190</v>
       </c>
@@ -8020,18 +8031,18 @@
         <v>790</v>
       </c>
       <c r="F138" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Yes</v>
       </c>
       <c r="G138" t="s">
         <v>795</v>
       </c>
       <c r="J138">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>136</v>
       </c>
     </row>
-    <row r="139" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A139" t="s">
         <v>191</v>
       </c>
@@ -8057,18 +8068,18 @@
         <v>768</v>
       </c>
       <c r="E139" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="F139" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Yes</v>
       </c>
       <c r="J139">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>137</v>
       </c>
     </row>
-    <row r="140" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A140" t="s">
         <v>192</v>
       </c>
@@ -8094,18 +8105,18 @@
         <v>768</v>
       </c>
       <c r="E140" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="F140" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Yes</v>
       </c>
       <c r="J140">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>138</v>
       </c>
     </row>
-    <row r="141" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A141" t="s">
         <v>193</v>
       </c>
@@ -8125,19 +8136,22 @@
 )</f>
         <v/>
       </c>
+      <c r="D141" t="s">
+        <v>9</v>
+      </c>
       <c r="E141" t="s">
         <v>797</v>
       </c>
       <c r="F141" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Yes</v>
       </c>
       <c r="J141">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>139</v>
       </c>
     </row>
-    <row r="142" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A142" t="s">
         <v>194</v>
       </c>
@@ -8158,47 +8172,29 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>No</v>
       </c>
       <c r="J142">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>140</v>
       </c>
     </row>
-    <row r="143" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A143" t="s">
         <v>195</v>
       </c>
       <c r="B143" s="2"/>
-      <c r="C143" s="2" t="str">
-        <f>IFERROR(
-  INDEX(Sheet1!$B$1:$N$1,
-    MATCH(B143,
-      INDEX(Sheet1!$B$2:$N$170,
-        MATCH($A143,Sheet1!$A$2:$A$170,0),
-        0
-      ),
-      0
-    )
-  ),
-  ""
-)</f>
-        <v/>
-      </c>
-      <c r="E143" t="s">
-        <v>798</v>
-      </c>
+      <c r="C143" s="2"/>
       <c r="F143" t="str">
-        <f t="shared" si="6"/>
-        <v>Yes</v>
+        <f t="shared" si="8"/>
+        <v>No</v>
       </c>
       <c r="J143">
-        <f t="shared" si="8"/>
         <v>141</v>
       </c>
     </row>
-    <row r="144" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A144" t="s">
         <v>196</v>
       </c>
@@ -8219,15 +8215,15 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>No</v>
       </c>
       <c r="J144">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="J144:J171" si="10">IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(A144,"GPIO",""),"号","")),"")</f>
         <v>142</v>
       </c>
     </row>
-    <row r="145" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A145" t="s">
         <v>197</v>
       </c>
@@ -8256,18 +8252,18 @@
         <v>717</v>
       </c>
       <c r="F145" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Yes</v>
       </c>
       <c r="G145" t="s">
         <v>770</v>
       </c>
       <c r="J145">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>143</v>
       </c>
     </row>
-    <row r="146" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A146" t="s">
         <v>198</v>
       </c>
@@ -8296,18 +8292,18 @@
         <v>718</v>
       </c>
       <c r="F146" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Yes</v>
       </c>
       <c r="G146" t="s">
         <v>770</v>
       </c>
       <c r="J146">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>144</v>
       </c>
     </row>
-    <row r="147" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A147" t="s">
         <v>199</v>
       </c>
@@ -8336,18 +8332,18 @@
         <v>530</v>
       </c>
       <c r="F147" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Yes</v>
       </c>
       <c r="G147" t="s">
         <v>770</v>
       </c>
       <c r="J147">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>145</v>
       </c>
     </row>
-    <row r="148" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A148" t="s">
         <v>200</v>
       </c>
@@ -8376,18 +8372,18 @@
         <v>535</v>
       </c>
       <c r="F148" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Yes</v>
       </c>
       <c r="G148" t="s">
         <v>770</v>
       </c>
       <c r="J148">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>146</v>
       </c>
     </row>
-    <row r="149" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A149" t="s">
         <v>201</v>
       </c>
@@ -8408,21 +8404,21 @@
         <v/>
       </c>
       <c r="D149" t="s">
+        <v>820</v>
+      </c>
+      <c r="E149" t="s">
         <v>822</v>
       </c>
-      <c r="E149" t="s">
-        <v>824</v>
-      </c>
       <c r="F149" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Yes</v>
       </c>
       <c r="J149">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>147</v>
       </c>
     </row>
-    <row r="150" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A150" t="s">
         <v>202</v>
       </c>
@@ -8451,18 +8447,18 @@
         <v>693</v>
       </c>
       <c r="F150" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Yes</v>
       </c>
       <c r="G150" t="s">
         <v>770</v>
       </c>
       <c r="J150">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>148</v>
       </c>
     </row>
-    <row r="151" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A151" t="s">
         <v>203</v>
       </c>
@@ -8483,15 +8479,15 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>No</v>
       </c>
       <c r="J151">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>149</v>
       </c>
     </row>
-    <row r="152" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A152" t="s">
         <v>204</v>
       </c>
@@ -8520,18 +8516,18 @@
         <v>444</v>
       </c>
       <c r="F152" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Yes</v>
       </c>
       <c r="G152" t="s">
         <v>770</v>
       </c>
       <c r="J152">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>150</v>
       </c>
     </row>
-    <row r="153" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A153" t="s">
         <v>205</v>
       </c>
@@ -8560,18 +8556,18 @@
         <v>437</v>
       </c>
       <c r="F153" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Yes</v>
       </c>
       <c r="G153" t="s">
         <v>770</v>
       </c>
       <c r="J153">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>151</v>
       </c>
     </row>
-    <row r="154" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A154" t="s">
         <v>206</v>
       </c>
@@ -8591,19 +8587,22 @@
 )</f>
         <v/>
       </c>
+      <c r="D154" t="s">
+        <v>9</v>
+      </c>
       <c r="E154" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="F154" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Yes</v>
       </c>
       <c r="J154">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>152</v>
       </c>
     </row>
-    <row r="155" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A155" t="s">
         <v>207</v>
       </c>
@@ -8624,17 +8623,17 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>No</v>
       </c>
       <c r="J155">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>153</v>
       </c>
     </row>
-    <row r="156" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A156" t="s">
-        <v>208</v>
+        <v>836</v>
       </c>
       <c r="B156" s="2"/>
       <c r="C156" s="2" t="str">
@@ -8652,19 +8651,16 @@
 )</f>
         <v/>
       </c>
-      <c r="E156" t="s">
-        <v>801</v>
-      </c>
       <c r="F156" t="str">
-        <f t="shared" si="6"/>
-        <v>Yes</v>
+        <f t="shared" si="8"/>
+        <v>No</v>
       </c>
       <c r="J156">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>154</v>
       </c>
     </row>
-    <row r="157" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A157" t="s">
         <v>209</v>
       </c>
@@ -8685,15 +8681,15 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>No</v>
       </c>
       <c r="J157">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>155</v>
       </c>
     </row>
-    <row r="158" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A158" t="s">
         <v>210</v>
       </c>
@@ -8722,18 +8718,18 @@
         <v>694</v>
       </c>
       <c r="F158" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Yes</v>
       </c>
       <c r="G158" t="s">
         <v>770</v>
       </c>
       <c r="J158">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>156</v>
       </c>
     </row>
-    <row r="159" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A159" t="s">
         <v>211</v>
       </c>
@@ -8754,21 +8750,21 @@
         <v/>
       </c>
       <c r="D159" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="E159" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="F159" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Yes</v>
       </c>
       <c r="J159">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>157</v>
       </c>
     </row>
-    <row r="160" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A160" t="s">
         <v>212</v>
       </c>
@@ -8789,15 +8785,15 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>No</v>
       </c>
       <c r="J160">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>158</v>
       </c>
     </row>
-    <row r="161" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A161" t="s">
         <v>213</v>
       </c>
@@ -8826,18 +8822,18 @@
         <v>695</v>
       </c>
       <c r="F161" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>Yes</v>
       </c>
       <c r="G161" t="s">
         <v>770</v>
       </c>
       <c r="J161">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>159</v>
       </c>
     </row>
-    <row r="162" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A162" t="s">
         <v>214</v>
       </c>
@@ -8866,18 +8862,18 @@
         <v>696</v>
       </c>
       <c r="F162" t="str">
-        <f t="shared" ref="F162:F191" si="9">IF(E162&lt;&gt;"","Yes","No")</f>
+        <f t="shared" ref="F162:F193" si="11">IF(E162&lt;&gt;"","Yes","No")</f>
         <v>Yes</v>
       </c>
       <c r="G162" t="s">
         <v>770</v>
       </c>
       <c r="J162">
-        <f t="shared" ref="J162:J171" si="10">IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(A162,"GPIO",""),"号","")),"")</f>
+        <f t="shared" si="10"/>
         <v>160</v>
       </c>
     </row>
-    <row r="163" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A163" t="s">
         <v>215</v>
       </c>
@@ -8906,7 +8902,7 @@
         <v>697</v>
       </c>
       <c r="F163" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Yes</v>
       </c>
       <c r="G163" t="s">
@@ -8917,7 +8913,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="164" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A164" t="s">
         <v>216</v>
       </c>
@@ -8938,7 +8934,7 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>No</v>
       </c>
       <c r="J164">
@@ -8946,7 +8942,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="165" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A165" t="s">
         <v>217</v>
       </c>
@@ -8967,7 +8963,7 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>No</v>
       </c>
       <c r="J165">
@@ -8975,7 +8971,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="166" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A166" t="s">
         <v>218</v>
       </c>
@@ -8996,7 +8992,7 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>No</v>
       </c>
       <c r="J166">
@@ -9004,7 +9000,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="167" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A167" t="s">
         <v>219</v>
       </c>
@@ -9025,7 +9021,7 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>No</v>
       </c>
       <c r="J167">
@@ -9033,7 +9029,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="168" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A168" t="s">
         <v>220</v>
       </c>
@@ -9057,10 +9053,10 @@
         <v>9</v>
       </c>
       <c r="E168" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="F168" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Yes</v>
       </c>
       <c r="J168">
@@ -9068,7 +9064,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="169" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A169" t="s">
         <v>221</v>
       </c>
@@ -9092,10 +9088,10 @@
         <v>9</v>
       </c>
       <c r="E169" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="F169" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Yes</v>
       </c>
       <c r="J169">
@@ -9103,7 +9099,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="170" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A170" t="s">
         <v>222</v>
       </c>
@@ -9127,10 +9123,10 @@
         <v>9</v>
       </c>
       <c r="E170" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="F170" t="str">
-        <f>IF(E170&lt;&gt;"","Yes","No")</f>
+        <f t="shared" si="11"/>
         <v>Yes</v>
       </c>
       <c r="J170">
@@ -9138,7 +9134,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="171" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A171" t="s">
         <v>725</v>
       </c>
@@ -9146,7 +9142,7 @@
         <v>17</v>
       </c>
       <c r="F171" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>No</v>
       </c>
       <c r="J171" t="str">
@@ -9154,7 +9150,7 @@
         <v/>
       </c>
     </row>
-    <row r="172" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A172" t="s">
         <v>726</v>
       </c>
@@ -9162,11 +9158,11 @@
         <v>17</v>
       </c>
       <c r="F172" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>No</v>
       </c>
     </row>
-    <row r="173" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A173" t="s">
         <v>727</v>
       </c>
@@ -9174,11 +9170,11 @@
         <v>17</v>
       </c>
       <c r="F173" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>No</v>
       </c>
     </row>
-    <row r="174" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A174" t="s">
         <v>728</v>
       </c>
@@ -9186,11 +9182,11 @@
         <v>17</v>
       </c>
       <c r="F174" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>No</v>
       </c>
     </row>
-    <row r="175" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A175" t="s">
         <v>729</v>
       </c>
@@ -9198,11 +9194,11 @@
         <v>17</v>
       </c>
       <c r="F175" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>No</v>
       </c>
     </row>
-    <row r="176" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A176" t="s">
         <v>730</v>
       </c>
@@ -9210,11 +9206,11 @@
         <v>17</v>
       </c>
       <c r="F176" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>No</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A177" t="s">
         <v>731</v>
       </c>
@@ -9222,11 +9218,11 @@
         <v>17</v>
       </c>
       <c r="F177" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>No</v>
       </c>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A178" t="s">
         <v>732</v>
       </c>
@@ -9234,11 +9230,11 @@
         <v>17</v>
       </c>
       <c r="F178" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>No</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A179" t="s">
         <v>733</v>
       </c>
@@ -9246,11 +9242,11 @@
         <v>17</v>
       </c>
       <c r="F179" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>No</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A180" t="s">
         <v>734</v>
       </c>
@@ -9258,11 +9254,11 @@
         <v>17</v>
       </c>
       <c r="F180" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>No</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A181" t="s">
         <v>735</v>
       </c>
@@ -9270,11 +9266,11 @@
         <v>17</v>
       </c>
       <c r="F181" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>No</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A182" t="s">
         <v>736</v>
       </c>
@@ -9282,11 +9278,11 @@
         <v>17</v>
       </c>
       <c r="F182" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>No</v>
       </c>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A183" t="s">
         <v>737</v>
       </c>
@@ -9294,11 +9290,11 @@
         <v>17</v>
       </c>
       <c r="F183" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>No</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A184" t="s">
         <v>738</v>
       </c>
@@ -9306,11 +9302,11 @@
         <v>17</v>
       </c>
       <c r="F184" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>No</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A185" t="s">
         <v>739</v>
       </c>
@@ -9318,11 +9314,11 @@
         <v>17</v>
       </c>
       <c r="F185" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>No</v>
       </c>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A186" t="s">
         <v>740</v>
       </c>
@@ -9330,11 +9326,11 @@
         <v>17</v>
       </c>
       <c r="F186" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>No</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A187" t="s">
         <v>741</v>
       </c>
@@ -9342,11 +9338,11 @@
         <v>17</v>
       </c>
       <c r="F187" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>No</v>
       </c>
     </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A188" t="s">
         <v>742</v>
       </c>
@@ -9354,11 +9350,11 @@
         <v>17</v>
       </c>
       <c r="F188" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>No</v>
       </c>
     </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A189" t="s">
         <v>743</v>
       </c>
@@ -9366,11 +9362,11 @@
         <v>17</v>
       </c>
       <c r="F189" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>No</v>
       </c>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A190" t="s">
         <v>744</v>
       </c>
@@ -9378,11 +9374,11 @@
         <v>17</v>
       </c>
       <c r="F190" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>No</v>
       </c>
     </row>
-    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:6" hidden="1" x14ac:dyDescent="0.15">
       <c r="A191" t="s">
         <v>745</v>
       </c>
@@ -9390,14 +9386,19 @@
         <v>17</v>
       </c>
       <c r="F191" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>No</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J170" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J170">
-      <sortCondition ref="J1:J170"/>
+  <autoFilter ref="A1:J191" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="3">
+      <filters>
+        <filter val="PWM"/>
+      </filters>
+    </filterColumn>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J191">
+      <sortCondition ref="J1:J191"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -9427,18 +9428,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:I17"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="24.90625" customWidth="1"/>
-    <col min="2" max="2" width="23.08984375" customWidth="1"/>
-    <col min="3" max="3" width="16.08984375" customWidth="1"/>
+    <col min="1" max="1" width="24.875" customWidth="1"/>
+    <col min="2" max="2" width="23.125" customWidth="1"/>
+    <col min="3" max="3" width="16.125" customWidth="1"/>
     <col min="4" max="4" width="21" customWidth="1"/>
-    <col min="5" max="5" width="22.26953125" customWidth="1"/>
-    <col min="6" max="6" width="23.36328125" customWidth="1"/>
-    <col min="7" max="8" width="34.453125" customWidth="1"/>
+    <col min="5" max="5" width="22.25" customWidth="1"/>
+    <col min="6" max="6" width="23.375" customWidth="1"/>
+    <col min="7" max="8" width="34.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -9464,7 +9465,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -9490,7 +9491,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -9513,7 +9514,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
         <v>24</v>
       </c>
@@ -9533,7 +9534,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
         <v>53</v>
       </c>
@@ -9553,7 +9554,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
         <v>54</v>
       </c>
@@ -9564,7 +9565,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
         <v>51</v>
       </c>
@@ -9572,52 +9573,52 @@
         <v>37</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
         <v>769</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A12" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A13" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A14" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A15" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A16" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A17" t="s">
         <v>41</v>
       </c>
@@ -9631,20 +9632,20 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE7C012F-2AE2-4B89-9859-DB6E135ED35D}">
   <dimension ref="A1:N170"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="4" width="20.6328125" customWidth="1"/>
-    <col min="5" max="5" width="12.7265625" customWidth="1"/>
-    <col min="6" max="6" width="13.453125" customWidth="1"/>
-    <col min="7" max="7" width="16.7265625" customWidth="1"/>
-    <col min="8" max="8" width="11.08984375" customWidth="1"/>
+    <col min="1" max="4" width="20.625" customWidth="1"/>
+    <col min="5" max="5" width="12.75" customWidth="1"/>
+    <col min="6" max="6" width="13.5" customWidth="1"/>
+    <col min="7" max="7" width="16.75" customWidth="1"/>
+    <col min="8" max="8" width="11.125" customWidth="1"/>
     <col min="9" max="9" width="18" customWidth="1"/>
-    <col min="10" max="10" width="17.453125" customWidth="1"/>
-    <col min="12" max="12" width="14.08984375" customWidth="1"/>
-    <col min="13" max="13" width="12.36328125" customWidth="1"/>
+    <col min="10" max="10" width="17.5" customWidth="1"/>
+    <col min="12" max="12" width="14.125" customWidth="1"/>
+    <col min="13" max="13" width="12.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="3" t="s">
         <v>241</v>
       </c>
@@ -9688,7 +9689,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="4" t="s">
         <v>225</v>
       </c>
@@ -9716,7 +9717,7 @@
       <c r="M2" s="4"/>
       <c r="N2" s="4"/>
     </row>
-    <row r="3" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="4" t="s">
         <v>55</v>
       </c>
@@ -9746,7 +9747,7 @@
       <c r="M3" s="4"/>
       <c r="N3" s="4"/>
     </row>
-    <row r="4" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="4" t="s">
         <v>56</v>
       </c>
@@ -9774,7 +9775,7 @@
       <c r="M4" s="4"/>
       <c r="N4" s="4"/>
     </row>
-    <row r="5" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="4" t="s">
         <v>57</v>
       </c>
@@ -9806,7 +9807,7 @@
       <c r="M5" s="4"/>
       <c r="N5" s="4"/>
     </row>
-    <row r="6" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="4" t="s">
         <v>58</v>
       </c>
@@ -9836,7 +9837,7 @@
       <c r="M6" s="4"/>
       <c r="N6" s="4"/>
     </row>
-    <row r="7" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="4" t="s">
         <v>59</v>
       </c>
@@ -9868,7 +9869,7 @@
       <c r="M7" s="4"/>
       <c r="N7" s="4"/>
     </row>
-    <row r="8" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A8" s="4" t="s">
         <v>60</v>
       </c>
@@ -9900,7 +9901,7 @@
       <c r="M8" s="4"/>
       <c r="N8" s="4"/>
     </row>
-    <row r="9" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A9" s="4" t="s">
         <v>61</v>
       </c>
@@ -9932,7 +9933,7 @@
       <c r="M9" s="4"/>
       <c r="N9" s="4"/>
     </row>
-    <row r="10" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A10" s="4" t="s">
         <v>62</v>
       </c>
@@ -9970,7 +9971,7 @@
       </c>
       <c r="N10" s="4"/>
     </row>
-    <row r="11" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="4" t="s">
         <v>63</v>
       </c>
@@ -10006,7 +10007,7 @@
       </c>
       <c r="N11" s="4"/>
     </row>
-    <row r="12" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="4" t="s">
         <v>64</v>
       </c>
@@ -10044,7 +10045,7 @@
       </c>
       <c r="N12" s="4"/>
     </row>
-    <row r="13" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="4" t="s">
         <v>65</v>
       </c>
@@ -10078,7 +10079,7 @@
       <c r="M13" s="4"/>
       <c r="N13" s="4"/>
     </row>
-    <row r="14" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="4" t="s">
         <v>66</v>
       </c>
@@ -10112,7 +10113,7 @@
       <c r="M14" s="4"/>
       <c r="N14" s="4"/>
     </row>
-    <row r="15" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="4" t="s">
         <v>67</v>
       </c>
@@ -10146,7 +10147,7 @@
       <c r="M15" s="4"/>
       <c r="N15" s="4"/>
     </row>
-    <row r="16" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="4" t="s">
         <v>68</v>
       </c>
@@ -10176,7 +10177,7 @@
       <c r="M16" s="4"/>
       <c r="N16" s="4"/>
     </row>
-    <row r="17" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="4" t="s">
         <v>69</v>
       </c>
@@ -10206,7 +10207,7 @@
       <c r="M17" s="4"/>
       <c r="N17" s="4"/>
     </row>
-    <row r="18" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="4" t="s">
         <v>70</v>
       </c>
@@ -10238,7 +10239,7 @@
       <c r="M18" s="4"/>
       <c r="N18" s="4"/>
     </row>
-    <row r="19" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="4" t="s">
         <v>71</v>
       </c>
@@ -10270,7 +10271,7 @@
       <c r="M19" s="4"/>
       <c r="N19" s="4"/>
     </row>
-    <row r="20" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="4" t="s">
         <v>72</v>
       </c>
@@ -10306,7 +10307,7 @@
       <c r="M20" s="4"/>
       <c r="N20" s="4"/>
     </row>
-    <row r="21" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="4" t="s">
         <v>73</v>
       </c>
@@ -10342,7 +10343,7 @@
       <c r="M21" s="4"/>
       <c r="N21" s="4"/>
     </row>
-    <row r="22" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="4" t="s">
         <v>74</v>
       </c>
@@ -10378,7 +10379,7 @@
       <c r="M22" s="4"/>
       <c r="N22" s="4"/>
     </row>
-    <row r="23" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="4" t="s">
         <v>75</v>
       </c>
@@ -10414,7 +10415,7 @@
       <c r="M23" s="4"/>
       <c r="N23" s="4"/>
     </row>
-    <row r="24" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="4" t="s">
         <v>76</v>
       </c>
@@ -10454,7 +10455,7 @@
       <c r="M24" s="4"/>
       <c r="N24" s="4"/>
     </row>
-    <row r="25" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="4" t="s">
         <v>77</v>
       </c>
@@ -10494,7 +10495,7 @@
       <c r="M25" s="4"/>
       <c r="N25" s="4"/>
     </row>
-    <row r="26" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="4" t="s">
         <v>78</v>
       </c>
@@ -10532,7 +10533,7 @@
       </c>
       <c r="N26" s="4"/>
     </row>
-    <row r="27" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="4" t="s">
         <v>79</v>
       </c>
@@ -10572,7 +10573,7 @@
       </c>
       <c r="N27" s="4"/>
     </row>
-    <row r="28" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="4" t="s">
         <v>80</v>
       </c>
@@ -10614,7 +10615,7 @@
       </c>
       <c r="N28" s="4"/>
     </row>
-    <row r="29" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="4" t="s">
         <v>81</v>
       </c>
@@ -10656,7 +10657,7 @@
       </c>
       <c r="N29" s="4"/>
     </row>
-    <row r="30" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="4" t="s">
         <v>82</v>
       </c>
@@ -10690,7 +10691,7 @@
       </c>
       <c r="N30" s="4"/>
     </row>
-    <row r="31" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="4" t="s">
         <v>83</v>
       </c>
@@ -10730,7 +10731,7 @@
       </c>
       <c r="N31" s="4"/>
     </row>
-    <row r="32" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="4" t="s">
         <v>84</v>
       </c>
@@ -10772,7 +10773,7 @@
       </c>
       <c r="N32" s="4"/>
     </row>
-    <row r="33" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="4" t="s">
         <v>85</v>
       </c>
@@ -10812,7 +10813,7 @@
       </c>
       <c r="N33" s="4"/>
     </row>
-    <row r="34" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="4" t="s">
         <v>86</v>
       </c>
@@ -10846,7 +10847,7 @@
       </c>
       <c r="N34" s="4"/>
     </row>
-    <row r="35" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="4" t="s">
         <v>87</v>
       </c>
@@ -10876,7 +10877,7 @@
       </c>
       <c r="N35" s="4"/>
     </row>
-    <row r="36" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="4" t="s">
         <v>88</v>
       </c>
@@ -10914,7 +10915,7 @@
       <c r="M36" s="4"/>
       <c r="N36" s="4"/>
     </row>
-    <row r="37" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="4" t="s">
         <v>89</v>
       </c>
@@ -10950,7 +10951,7 @@
       <c r="M37" s="4"/>
       <c r="N37" s="4"/>
     </row>
-    <row r="38" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="4" t="s">
         <v>90</v>
       </c>
@@ -10982,7 +10983,7 @@
       <c r="M38" s="4"/>
       <c r="N38" s="4"/>
     </row>
-    <row r="39" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="4" t="s">
         <v>91</v>
       </c>
@@ -11014,7 +11015,7 @@
       <c r="M39" s="4"/>
       <c r="N39" s="4"/>
     </row>
-    <row r="40" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="4" t="s">
         <v>92</v>
       </c>
@@ -11048,7 +11049,7 @@
       <c r="M40" s="4"/>
       <c r="N40" s="4"/>
     </row>
-    <row r="41" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="4" t="s">
         <v>93</v>
       </c>
@@ -11082,7 +11083,7 @@
       <c r="M41" s="4"/>
       <c r="N41" s="4"/>
     </row>
-    <row r="42" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="4" t="s">
         <v>94</v>
       </c>
@@ -11108,7 +11109,7 @@
       <c r="M42" s="4"/>
       <c r="N42" s="4"/>
     </row>
-    <row r="43" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="4" t="s">
         <v>95</v>
       </c>
@@ -11136,7 +11137,7 @@
       <c r="M43" s="4"/>
       <c r="N43" s="4"/>
     </row>
-    <row r="44" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="4" t="s">
         <v>96</v>
       </c>
@@ -11164,7 +11165,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="45" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="4" t="s">
         <v>97</v>
       </c>
@@ -11192,7 +11193,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="46" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="4" t="s">
         <v>98</v>
       </c>
@@ -11216,7 +11217,7 @@
       <c r="M46" s="4"/>
       <c r="N46" s="4"/>
     </row>
-    <row r="47" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="4" t="s">
         <v>99</v>
       </c>
@@ -11240,7 +11241,7 @@
       <c r="M47" s="4"/>
       <c r="N47" s="4"/>
     </row>
-    <row r="48" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="4" t="s">
         <v>100</v>
       </c>
@@ -11266,7 +11267,7 @@
       <c r="M48" s="4"/>
       <c r="N48" s="4"/>
     </row>
-    <row r="49" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="4" t="s">
         <v>101</v>
       </c>
@@ -11292,7 +11293,7 @@
       <c r="M49" s="4"/>
       <c r="N49" s="4"/>
     </row>
-    <row r="50" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="4" t="s">
         <v>102</v>
       </c>
@@ -11322,7 +11323,7 @@
       <c r="M50" s="4"/>
       <c r="N50" s="4"/>
     </row>
-    <row r="51" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="4" t="s">
         <v>103</v>
       </c>
@@ -11356,7 +11357,7 @@
       <c r="M51" s="4"/>
       <c r="N51" s="4"/>
     </row>
-    <row r="52" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="4" t="s">
         <v>104</v>
       </c>
@@ -11390,7 +11391,7 @@
       <c r="M52" s="4"/>
       <c r="N52" s="4"/>
     </row>
-    <row r="53" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="4" t="s">
         <v>105</v>
       </c>
@@ -11424,7 +11425,7 @@
       <c r="M53" s="4"/>
       <c r="N53" s="4"/>
     </row>
-    <row r="54" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="4" t="s">
         <v>106</v>
       </c>
@@ -11458,7 +11459,7 @@
       <c r="M54" s="4"/>
       <c r="N54" s="4"/>
     </row>
-    <row r="55" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="4" t="s">
         <v>107</v>
       </c>
@@ -11494,7 +11495,7 @@
       <c r="M55" s="4"/>
       <c r="N55" s="4"/>
     </row>
-    <row r="56" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="4" t="s">
         <v>108</v>
       </c>
@@ -11534,7 +11535,7 @@
       </c>
       <c r="N56" s="4"/>
     </row>
-    <row r="57" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="4" t="s">
         <v>109</v>
       </c>
@@ -11574,7 +11575,7 @@
       </c>
       <c r="N57" s="4"/>
     </row>
-    <row r="58" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="4" t="s">
         <v>110</v>
       </c>
@@ -11616,7 +11617,7 @@
       </c>
       <c r="N58" s="4"/>
     </row>
-    <row r="59" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="4" t="s">
         <v>111</v>
       </c>
@@ -11656,7 +11657,7 @@
       </c>
       <c r="N59" s="4"/>
     </row>
-    <row r="60" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="4" t="s">
         <v>112</v>
       </c>
@@ -11698,7 +11699,7 @@
       </c>
       <c r="N60" s="4"/>
     </row>
-    <row r="61" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A61" s="4" t="s">
         <v>113</v>
       </c>
@@ -11740,7 +11741,7 @@
       </c>
       <c r="N61" s="4"/>
     </row>
-    <row r="62" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="4" t="s">
         <v>114</v>
       </c>
@@ -11782,7 +11783,7 @@
       </c>
       <c r="N62" s="4"/>
     </row>
-    <row r="63" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="4" t="s">
         <v>115</v>
       </c>
@@ -11822,7 +11823,7 @@
       </c>
       <c r="N63" s="4"/>
     </row>
-    <row r="64" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="4" t="s">
         <v>116</v>
       </c>
@@ -11860,7 +11861,7 @@
       <c r="M64" s="4"/>
       <c r="N64" s="4"/>
     </row>
-    <row r="65" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A65" s="4" t="s">
         <v>117</v>
       </c>
@@ -11900,7 +11901,7 @@
       </c>
       <c r="N65" s="4"/>
     </row>
-    <row r="66" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A66" s="4" t="s">
         <v>118</v>
       </c>
@@ -11938,7 +11939,7 @@
       </c>
       <c r="N66" s="4"/>
     </row>
-    <row r="67" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A67" s="4" t="s">
         <v>119</v>
       </c>
@@ -11976,7 +11977,7 @@
       </c>
       <c r="N67" s="4"/>
     </row>
-    <row r="68" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A68" s="4" t="s">
         <v>120</v>
       </c>
@@ -12012,7 +12013,7 @@
       </c>
       <c r="N68" s="4"/>
     </row>
-    <row r="69" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A69" s="4" t="s">
         <v>121</v>
       </c>
@@ -12040,7 +12041,7 @@
       <c r="M69" s="4"/>
       <c r="N69" s="4"/>
     </row>
-    <row r="70" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A70" s="4" t="s">
         <v>122</v>
       </c>
@@ -12068,7 +12069,7 @@
       <c r="M70" s="4"/>
       <c r="N70" s="4"/>
     </row>
-    <row r="71" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A71" s="4" t="s">
         <v>123</v>
       </c>
@@ -12100,7 +12101,7 @@
       </c>
       <c r="N71" s="4"/>
     </row>
-    <row r="72" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A72" s="4" t="s">
         <v>124</v>
       </c>
@@ -12134,7 +12135,7 @@
       </c>
       <c r="N72" s="4"/>
     </row>
-    <row r="73" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A73" s="4" t="s">
         <v>125</v>
       </c>
@@ -12168,7 +12169,7 @@
       </c>
       <c r="N73" s="4"/>
     </row>
-    <row r="74" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A74" s="4" t="s">
         <v>126</v>
       </c>
@@ -12200,7 +12201,7 @@
       </c>
       <c r="N74" s="4"/>
     </row>
-    <row r="75" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A75" s="4" t="s">
         <v>127</v>
       </c>
@@ -12234,7 +12235,7 @@
       <c r="M75" s="4"/>
       <c r="N75" s="4"/>
     </row>
-    <row r="76" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A76" s="4" t="s">
         <v>128</v>
       </c>
@@ -12262,7 +12263,7 @@
       <c r="M76" s="4"/>
       <c r="N76" s="4"/>
     </row>
-    <row r="77" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A77" s="4" t="s">
         <v>129</v>
       </c>
@@ -12290,7 +12291,7 @@
       <c r="M77" s="4"/>
       <c r="N77" s="4"/>
     </row>
-    <row r="78" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A78" s="4" t="s">
         <v>130</v>
       </c>
@@ -12318,7 +12319,7 @@
       <c r="M78" s="4"/>
       <c r="N78" s="4"/>
     </row>
-    <row r="79" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A79" s="4" t="s">
         <v>131</v>
       </c>
@@ -12344,7 +12345,7 @@
       <c r="M79" s="4"/>
       <c r="N79" s="4"/>
     </row>
-    <row r="80" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A80" s="4" t="s">
         <v>132</v>
       </c>
@@ -12370,7 +12371,7 @@
       <c r="M80" s="4"/>
       <c r="N80" s="4"/>
     </row>
-    <row r="81" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A81" s="4" t="s">
         <v>133</v>
       </c>
@@ -12396,7 +12397,7 @@
       <c r="M81" s="4"/>
       <c r="N81" s="4"/>
     </row>
-    <row r="82" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A82" s="4" t="s">
         <v>134</v>
       </c>
@@ -12422,7 +12423,7 @@
       <c r="M82" s="4"/>
       <c r="N82" s="4"/>
     </row>
-    <row r="83" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A83" s="4" t="s">
         <v>135</v>
       </c>
@@ -12446,7 +12447,7 @@
       <c r="M83" s="4"/>
       <c r="N83" s="4"/>
     </row>
-    <row r="84" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A84" s="4" t="s">
         <v>136</v>
       </c>
@@ -12468,7 +12469,7 @@
       <c r="M84" s="4"/>
       <c r="N84" s="4"/>
     </row>
-    <row r="85" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A85" s="4" t="s">
         <v>137</v>
       </c>
@@ -12490,7 +12491,7 @@
       <c r="M85" s="4"/>
       <c r="N85" s="4"/>
     </row>
-    <row r="86" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A86" s="4" t="s">
         <v>138</v>
       </c>
@@ -12518,7 +12519,7 @@
       </c>
       <c r="N86" s="4"/>
     </row>
-    <row r="87" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A87" s="4" t="s">
         <v>139</v>
       </c>
@@ -12548,7 +12549,7 @@
       </c>
       <c r="N87" s="4"/>
     </row>
-    <row r="88" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A88" s="4" t="s">
         <v>140</v>
       </c>
@@ -12578,7 +12579,7 @@
       </c>
       <c r="N88" s="4"/>
     </row>
-    <row r="89" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A89" s="4" t="s">
         <v>141</v>
       </c>
@@ -12610,7 +12611,7 @@
       </c>
       <c r="N89" s="4"/>
     </row>
-    <row r="90" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A90" s="4" t="s">
         <v>142</v>
       </c>
@@ -12636,7 +12637,7 @@
       <c r="M90" s="4"/>
       <c r="N90" s="4"/>
     </row>
-    <row r="91" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A91" s="4" t="s">
         <v>143</v>
       </c>
@@ -12664,7 +12665,7 @@
       <c r="M91" s="4"/>
       <c r="N91" s="4"/>
     </row>
-    <row r="92" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A92" s="4" t="s">
         <v>144</v>
       </c>
@@ -12692,7 +12693,7 @@
       <c r="M92" s="4"/>
       <c r="N92" s="4"/>
     </row>
-    <row r="93" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A93" s="4" t="s">
         <v>145</v>
       </c>
@@ -12728,7 +12729,7 @@
       </c>
       <c r="N93" s="4"/>
     </row>
-    <row r="94" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A94" s="4" t="s">
         <v>146</v>
       </c>
@@ -12764,7 +12765,7 @@
       </c>
       <c r="N94" s="4"/>
     </row>
-    <row r="95" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A95" s="4" t="s">
         <v>147</v>
       </c>
@@ -12796,7 +12797,7 @@
       </c>
       <c r="N95" s="4"/>
     </row>
-    <row r="96" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A96" s="4" t="s">
         <v>148</v>
       </c>
@@ -12828,7 +12829,7 @@
       </c>
       <c r="N96" s="4"/>
     </row>
-    <row r="97" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A97" s="4" t="s">
         <v>149</v>
       </c>
@@ -12852,7 +12853,7 @@
       <c r="M97" s="4"/>
       <c r="N97" s="4"/>
     </row>
-    <row r="98" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A98" s="4" t="s">
         <v>150</v>
       </c>
@@ -12878,7 +12879,7 @@
       <c r="M98" s="4"/>
       <c r="N98" s="4"/>
     </row>
-    <row r="99" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A99" s="4" t="s">
         <v>151</v>
       </c>
@@ -12904,7 +12905,7 @@
       <c r="M99" s="4"/>
       <c r="N99" s="4"/>
     </row>
-    <row r="100" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A100" s="4" t="s">
         <v>152</v>
       </c>
@@ -12930,7 +12931,7 @@
       <c r="M100" s="4"/>
       <c r="N100" s="4"/>
     </row>
-    <row r="101" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A101" s="4" t="s">
         <v>153</v>
       </c>
@@ -12954,7 +12955,7 @@
       <c r="M101" s="4"/>
       <c r="N101" s="4"/>
     </row>
-    <row r="102" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A102" s="4" t="s">
         <v>154</v>
       </c>
@@ -12982,7 +12983,7 @@
       <c r="M102" s="4"/>
       <c r="N102" s="4"/>
     </row>
-    <row r="103" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A103" s="4" t="s">
         <v>155</v>
       </c>
@@ -13010,7 +13011,7 @@
       <c r="M103" s="4"/>
       <c r="N103" s="4"/>
     </row>
-    <row r="104" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A104" s="4" t="s">
         <v>156</v>
       </c>
@@ -13038,7 +13039,7 @@
       <c r="M104" s="4"/>
       <c r="N104" s="4"/>
     </row>
-    <row r="105" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A105" s="4" t="s">
         <v>157</v>
       </c>
@@ -13066,7 +13067,7 @@
       <c r="M105" s="4"/>
       <c r="N105" s="4"/>
     </row>
-    <row r="106" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A106" s="4" t="s">
         <v>158</v>
       </c>
@@ -13098,7 +13099,7 @@
       <c r="M106" s="4"/>
       <c r="N106" s="4"/>
     </row>
-    <row r="107" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A107" s="4" t="s">
         <v>159</v>
       </c>
@@ -13132,7 +13133,7 @@
       <c r="M107" s="4"/>
       <c r="N107" s="4"/>
     </row>
-    <row r="108" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A108" s="4" t="s">
         <v>160</v>
       </c>
@@ -13162,7 +13163,7 @@
       <c r="M108" s="4"/>
       <c r="N108" s="4"/>
     </row>
-    <row r="109" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A109" s="4" t="s">
         <v>161</v>
       </c>
@@ -13192,7 +13193,7 @@
       <c r="M109" s="4"/>
       <c r="N109" s="4"/>
     </row>
-    <row r="110" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A110" s="4" t="s">
         <v>162</v>
       </c>
@@ -13218,7 +13219,7 @@
       <c r="M110" s="4"/>
       <c r="N110" s="4"/>
     </row>
-    <row r="111" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A111" s="4" t="s">
         <v>163</v>
       </c>
@@ -13242,7 +13243,7 @@
       <c r="M111" s="4"/>
       <c r="N111" s="4"/>
     </row>
-    <row r="112" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A112" s="4" t="s">
         <v>164</v>
       </c>
@@ -13268,7 +13269,7 @@
       <c r="M112" s="4"/>
       <c r="N112" s="4"/>
     </row>
-    <row r="113" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A113" s="4" t="s">
         <v>165</v>
       </c>
@@ -13294,7 +13295,7 @@
       <c r="M113" s="4"/>
       <c r="N113" s="4"/>
     </row>
-    <row r="114" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A114" s="4" t="s">
         <v>166</v>
       </c>
@@ -13320,7 +13321,7 @@
       <c r="M114" s="4"/>
       <c r="N114" s="4"/>
     </row>
-    <row r="115" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A115" s="4" t="s">
         <v>167</v>
       </c>
@@ -13344,7 +13345,7 @@
       <c r="M115" s="4"/>
       <c r="N115" s="4"/>
     </row>
-    <row r="116" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A116" s="4" t="s">
         <v>168</v>
       </c>
@@ -13368,7 +13369,7 @@
       <c r="M116" s="4"/>
       <c r="N116" s="4"/>
     </row>
-    <row r="117" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A117" s="4" t="s">
         <v>169</v>
       </c>
@@ -13396,7 +13397,7 @@
       <c r="M117" s="4"/>
       <c r="N117" s="4"/>
     </row>
-    <row r="118" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A118" s="4" t="s">
         <v>170</v>
       </c>
@@ -13424,7 +13425,7 @@
       <c r="M118" s="4"/>
       <c r="N118" s="4"/>
     </row>
-    <row r="119" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A119" s="4" t="s">
         <v>171</v>
       </c>
@@ -13450,7 +13451,7 @@
       <c r="M119" s="4"/>
       <c r="N119" s="4"/>
     </row>
-    <row r="120" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A120" s="4" t="s">
         <v>172</v>
       </c>
@@ -13476,7 +13477,7 @@
       <c r="M120" s="4"/>
       <c r="N120" s="4"/>
     </row>
-    <row r="121" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A121" s="4" t="s">
         <v>173</v>
       </c>
@@ -13502,7 +13503,7 @@
       <c r="M121" s="4"/>
       <c r="N121" s="4"/>
     </row>
-    <row r="122" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A122" s="4" t="s">
         <v>174</v>
       </c>
@@ -13528,7 +13529,7 @@
       <c r="M122" s="4"/>
       <c r="N122" s="4"/>
     </row>
-    <row r="123" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A123" s="4" t="s">
         <v>175</v>
       </c>
@@ -13554,7 +13555,7 @@
       <c r="M123" s="4"/>
       <c r="N123" s="4"/>
     </row>
-    <row r="124" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A124" s="4" t="s">
         <v>176</v>
       </c>
@@ -13582,7 +13583,7 @@
       <c r="M124" s="4"/>
       <c r="N124" s="4"/>
     </row>
-    <row r="125" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A125" s="4" t="s">
         <v>177</v>
       </c>
@@ -13610,7 +13611,7 @@
       <c r="M125" s="4"/>
       <c r="N125" s="4"/>
     </row>
-    <row r="126" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A126" s="4" t="s">
         <v>178</v>
       </c>
@@ -13638,7 +13639,7 @@
       <c r="M126" s="4"/>
       <c r="N126" s="4"/>
     </row>
-    <row r="127" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A127" s="4" t="s">
         <v>179</v>
       </c>
@@ -13668,7 +13669,7 @@
       <c r="M127" s="4"/>
       <c r="N127" s="4"/>
     </row>
-    <row r="128" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A128" s="4" t="s">
         <v>180</v>
       </c>
@@ -13696,7 +13697,7 @@
       <c r="M128" s="4"/>
       <c r="N128" s="4"/>
     </row>
-    <row r="129" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A129" s="4" t="s">
         <v>181</v>
       </c>
@@ -13722,7 +13723,7 @@
       <c r="M129" s="4"/>
       <c r="N129" s="4"/>
     </row>
-    <row r="130" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A130" s="4" t="s">
         <v>182</v>
       </c>
@@ -13748,7 +13749,7 @@
       <c r="M130" s="4"/>
       <c r="N130" s="4"/>
     </row>
-    <row r="131" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A131" s="4" t="s">
         <v>183</v>
       </c>
@@ -13774,7 +13775,7 @@
       <c r="M131" s="4"/>
       <c r="N131" s="4"/>
     </row>
-    <row r="132" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A132" s="4" t="s">
         <v>184</v>
       </c>
@@ -13800,7 +13801,7 @@
       <c r="M132" s="4"/>
       <c r="N132" s="4"/>
     </row>
-    <row r="133" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A133" s="4" t="s">
         <v>185</v>
       </c>
@@ -13826,7 +13827,7 @@
       <c r="M133" s="4"/>
       <c r="N133" s="4"/>
     </row>
-    <row r="134" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A134" s="4" t="s">
         <v>186</v>
       </c>
@@ -13852,7 +13853,7 @@
       <c r="M134" s="4"/>
       <c r="N134" s="4"/>
     </row>
-    <row r="135" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A135" s="4" t="s">
         <v>187</v>
       </c>
@@ -13874,7 +13875,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="136" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A136" s="4" t="s">
         <v>188</v>
       </c>
@@ -13900,7 +13901,7 @@
       <c r="M136" s="4"/>
       <c r="N136" s="4"/>
     </row>
-    <row r="137" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A137" s="4" t="s">
         <v>189</v>
       </c>
@@ -13928,7 +13929,7 @@
       <c r="M137" s="4"/>
       <c r="N137" s="4"/>
     </row>
-    <row r="138" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A138" s="4" t="s">
         <v>190</v>
       </c>
@@ -13956,7 +13957,7 @@
       <c r="M138" s="4"/>
       <c r="N138" s="4"/>
     </row>
-    <row r="139" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A139" s="4" t="s">
         <v>191</v>
       </c>
@@ -13986,7 +13987,7 @@
       <c r="M139" s="4"/>
       <c r="N139" s="4"/>
     </row>
-    <row r="140" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A140" s="4" t="s">
         <v>192</v>
       </c>
@@ -14014,7 +14015,7 @@
       <c r="M140" s="4"/>
       <c r="N140" s="4"/>
     </row>
-    <row r="141" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A141" s="4" t="s">
         <v>193</v>
       </c>
@@ -14040,7 +14041,7 @@
       <c r="M141" s="4"/>
       <c r="N141" s="4"/>
     </row>
-    <row r="142" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A142" s="4" t="s">
         <v>194</v>
       </c>
@@ -14066,7 +14067,7 @@
       <c r="M142" s="4"/>
       <c r="N142" s="4"/>
     </row>
-    <row r="143" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A143" s="4" t="s">
         <v>195</v>
       </c>
@@ -14092,7 +14093,7 @@
       <c r="M143" s="4"/>
       <c r="N143" s="4"/>
     </row>
-    <row r="144" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A144" s="4" t="s">
         <v>196</v>
       </c>
@@ -14118,7 +14119,7 @@
       <c r="M144" s="4"/>
       <c r="N144" s="4"/>
     </row>
-    <row r="145" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A145" s="4" t="s">
         <v>197</v>
       </c>
@@ -14142,7 +14143,7 @@
       <c r="M145" s="4"/>
       <c r="N145" s="4"/>
     </row>
-    <row r="146" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A146" s="4" t="s">
         <v>198</v>
       </c>
@@ -14166,7 +14167,7 @@
       <c r="M146" s="4"/>
       <c r="N146" s="4"/>
     </row>
-    <row r="147" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A147" s="4" t="s">
         <v>199</v>
       </c>
@@ -14190,7 +14191,7 @@
       <c r="M147" s="4"/>
       <c r="N147" s="4"/>
     </row>
-    <row r="148" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A148" s="4" t="s">
         <v>200</v>
       </c>
@@ -14214,7 +14215,7 @@
       <c r="M148" s="4"/>
       <c r="N148" s="4"/>
     </row>
-    <row r="149" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A149" s="4" t="s">
         <v>201</v>
       </c>
@@ -14238,7 +14239,7 @@
       <c r="M149" s="4"/>
       <c r="N149" s="4"/>
     </row>
-    <row r="150" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A150" s="4" t="s">
         <v>202</v>
       </c>
@@ -14262,7 +14263,7 @@
       <c r="M150" s="4"/>
       <c r="N150" s="4"/>
     </row>
-    <row r="151" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A151" s="4" t="s">
         <v>203</v>
       </c>
@@ -14286,7 +14287,7 @@
       <c r="M151" s="4"/>
       <c r="N151" s="4"/>
     </row>
-    <row r="152" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A152" s="4" t="s">
         <v>204</v>
       </c>
@@ -14310,7 +14311,7 @@
       <c r="M152" s="4"/>
       <c r="N152" s="4"/>
     </row>
-    <row r="153" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A153" s="4" t="s">
         <v>205</v>
       </c>
@@ -14334,7 +14335,7 @@
       <c r="M153" s="4"/>
       <c r="N153" s="4"/>
     </row>
-    <row r="154" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A154" s="4" t="s">
         <v>206</v>
       </c>
@@ -14358,7 +14359,7 @@
       <c r="M154" s="4"/>
       <c r="N154" s="4"/>
     </row>
-    <row r="155" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A155" s="4" t="s">
         <v>207</v>
       </c>
@@ -14382,7 +14383,7 @@
       <c r="M155" s="4"/>
       <c r="N155" s="4"/>
     </row>
-    <row r="156" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A156" s="4" t="s">
         <v>208</v>
       </c>
@@ -14406,7 +14407,7 @@
       <c r="M156" s="4"/>
       <c r="N156" s="4"/>
     </row>
-    <row r="157" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A157" s="4" t="s">
         <v>209</v>
       </c>
@@ -14430,7 +14431,7 @@
       <c r="M157" s="4"/>
       <c r="N157" s="4"/>
     </row>
-    <row r="158" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A158" s="4" t="s">
         <v>210</v>
       </c>
@@ -14454,7 +14455,7 @@
       <c r="M158" s="4"/>
       <c r="N158" s="4"/>
     </row>
-    <row r="159" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A159" s="4" t="s">
         <v>211</v>
       </c>
@@ -14478,7 +14479,7 @@
       <c r="M159" s="4"/>
       <c r="N159" s="4"/>
     </row>
-    <row r="160" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A160" s="4" t="s">
         <v>212</v>
       </c>
@@ -14502,7 +14503,7 @@
       <c r="M160" s="4"/>
       <c r="N160" s="4"/>
     </row>
-    <row r="161" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A161" s="4" t="s">
         <v>213</v>
       </c>
@@ -14526,7 +14527,7 @@
       <c r="M161" s="4"/>
       <c r="N161" s="4"/>
     </row>
-    <row r="162" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A162" s="4" t="s">
         <v>214</v>
       </c>
@@ -14550,7 +14551,7 @@
       <c r="M162" s="4"/>
       <c r="N162" s="4"/>
     </row>
-    <row r="163" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A163" s="4" t="s">
         <v>215</v>
       </c>
@@ -14574,7 +14575,7 @@
       <c r="M163" s="4"/>
       <c r="N163" s="4"/>
     </row>
-    <row r="164" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A164" s="4" t="s">
         <v>216</v>
       </c>
@@ -14598,7 +14599,7 @@
       <c r="M164" s="4"/>
       <c r="N164" s="4"/>
     </row>
-    <row r="165" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A165" s="4" t="s">
         <v>217</v>
       </c>
@@ -14622,7 +14623,7 @@
       <c r="M165" s="4"/>
       <c r="N165" s="4"/>
     </row>
-    <row r="166" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A166" s="4" t="s">
         <v>218</v>
       </c>
@@ -14646,7 +14647,7 @@
       <c r="M166" s="4"/>
       <c r="N166" s="4"/>
     </row>
-    <row r="167" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A167" s="4" t="s">
         <v>219</v>
       </c>
@@ -14670,7 +14671,7 @@
       <c r="M167" s="4"/>
       <c r="N167" s="4"/>
     </row>
-    <row r="168" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A168" s="4" t="s">
         <v>220</v>
       </c>
@@ -14694,7 +14695,7 @@
       <c r="M168" s="4"/>
       <c r="N168" s="4"/>
     </row>
-    <row r="169" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A169" s="4" t="s">
         <v>221</v>
       </c>
@@ -14718,7 +14719,7 @@
       <c r="M169" s="4"/>
       <c r="N169" s="4"/>
     </row>
-    <row r="170" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A170" s="4" t="s">
         <v>222</v>
       </c>

--- a/28388motherboard/TMS320F28388D_PinMap.xlsx
+++ b/28388motherboard/TMS320F28388D_PinMap.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\codefile\28388Board\mmlab-12PhaseDrive-388Slave\28388motherboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A5699F5-47FA-4E7A-B7DE-99E0E47383BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{597D13C1-D3F8-4A04-8052-750172845AA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38400" yWindow="3900" windowWidth="38700" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="38700" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PinMap" sheetId="1" r:id="rId1"/>
@@ -3072,13 +3072,11 @@
         <v>719</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
-        <v>223</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>255</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="B2" s="2"/>
       <c r="C2" s="2" t="str">
         <f>IFERROR(
   INDEX(Sheet1!$B$1:$N$1,
@@ -3092,13 +3090,13 @@
   ),
   ""
 )</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="E2" t="s">
-        <v>676</v>
+        <v>799</v>
       </c>
       <c r="F2" t="str">
         <f t="shared" ref="F2:F33" si="0">IF(E2&lt;&gt;"","Yes","No")</f>
@@ -3106,16 +3104,14 @@
       </c>
       <c r="J2">
         <f t="shared" ref="J2:J33" si="1">IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(A2,"GPIO",""),"号","")),"")</f>
-        <v>0</v>
+        <v>152</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
-        <v>224</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>260</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="B3" s="2"/>
       <c r="C3" s="2" t="str">
         <f>IFERROR(
   INDEX(Sheet1!$B$1:$N$1,
@@ -3129,13 +3125,13 @@
   ),
   ""
 )</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="D3" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="E3" t="s">
-        <v>677</v>
+        <v>835</v>
       </c>
       <c r="F3" t="str">
         <f t="shared" si="0"/>
@@ -3143,16 +3139,14 @@
       </c>
       <c r="J3">
         <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
-        <v>56</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>266</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="B4" s="2"/>
       <c r="C4" s="2" t="str">
         <f>IFERROR(
   INDEX(Sheet1!$B$1:$N$1,
@@ -3166,13 +3160,13 @@
   ),
   ""
 )</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="D4" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="E4" t="s">
-        <v>678</v>
+        <v>825</v>
       </c>
       <c r="F4" t="str">
         <f t="shared" si="0"/>
@@ -3180,16 +3174,14 @@
       </c>
       <c r="J4">
         <f t="shared" si="1"/>
-        <v>2</v>
+        <v>109</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
-        <v>57</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>271</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="B5" s="2"/>
       <c r="C5" s="2" t="str">
         <f>IFERROR(
   INDEX(Sheet1!$B$1:$N$1,
@@ -3203,13 +3195,13 @@
   ),
   ""
 )</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="D5" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="E5" t="s">
-        <v>679</v>
+        <v>824</v>
       </c>
       <c r="F5" t="str">
         <f t="shared" si="0"/>
@@ -3217,16 +3209,14 @@
       </c>
       <c r="J5">
         <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
-        <v>58</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>277</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="B6" s="2"/>
       <c r="C6" s="2" t="str">
         <f>IFERROR(
   INDEX(Sheet1!$B$1:$N$1,
@@ -3240,13 +3230,13 @@
   ),
   ""
 )</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="D6" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="E6" t="s">
-        <v>680</v>
+        <v>831</v>
       </c>
       <c r="F6" t="str">
         <f t="shared" si="0"/>
@@ -3254,16 +3244,14 @@
       </c>
       <c r="J6">
         <f t="shared" si="1"/>
-        <v>4</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
-        <v>59</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>283</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="B7" s="2"/>
       <c r="C7" s="2" t="str">
         <f>IFERROR(
   INDEX(Sheet1!$B$1:$N$1,
@@ -3277,13 +3265,13 @@
   ),
   ""
 )</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="D7" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="E7" t="s">
-        <v>681</v>
+        <v>830</v>
       </c>
       <c r="F7" t="str">
         <f t="shared" si="0"/>
@@ -3291,16 +3279,14 @@
       </c>
       <c r="J7">
         <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
-        <v>60</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>289</v>
-      </c>
+        <v>171</v>
+      </c>
+      <c r="B8" s="2"/>
       <c r="C8" s="2" t="str">
         <f>IFERROR(
   INDEX(Sheet1!$B$1:$N$1,
@@ -3314,13 +3300,13 @@
   ),
   ""
 )</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="D8" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="E8" t="s">
-        <v>682</v>
+        <v>800</v>
       </c>
       <c r="F8" t="str">
         <f t="shared" si="0"/>
@@ -3328,16 +3314,14 @@
       </c>
       <c r="J8">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>117</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
-        <v>61</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>296</v>
-      </c>
+        <v>82</v>
+      </c>
+      <c r="B9" s="2"/>
       <c r="C9" s="2" t="str">
         <f>IFERROR(
   INDEX(Sheet1!$B$1:$N$1,
@@ -3351,13 +3335,13 @@
   ),
   ""
 )</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="D9" t="s">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="E9" t="s">
-        <v>683</v>
+        <v>833</v>
       </c>
       <c r="F9" t="str">
         <f t="shared" si="0"/>
@@ -3365,15 +3349,15 @@
       </c>
       <c r="J9">
         <f t="shared" si="1"/>
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>303</v>
+        <v>359</v>
       </c>
       <c r="C10" s="2" t="str">
         <f>IFERROR(
@@ -3388,13 +3372,13 @@
   ),
   ""
 )</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D10" t="s">
         <v>24</v>
       </c>
       <c r="E10" t="s">
-        <v>684</v>
+        <v>762</v>
       </c>
       <c r="F10" t="str">
         <f t="shared" si="0"/>
@@ -3402,15 +3386,15 @@
       </c>
       <c r="J10">
         <f t="shared" si="1"/>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>309</v>
+        <v>365</v>
       </c>
       <c r="C11" s="2" t="str">
         <f>IFERROR(
@@ -3425,13 +3409,13 @@
   ),
   ""
 )</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D11" t="s">
         <v>24</v>
       </c>
       <c r="E11" t="s">
-        <v>685</v>
+        <v>763</v>
       </c>
       <c r="F11" t="str">
         <f t="shared" si="0"/>
@@ -3439,15 +3423,15 @@
       </c>
       <c r="J11">
         <f t="shared" si="1"/>
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A12" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>316</v>
+        <v>371</v>
       </c>
       <c r="C12" s="2" t="str">
         <f>IFERROR(
@@ -3462,13 +3446,13 @@
   ),
   ""
 )</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D12" t="s">
         <v>24</v>
       </c>
       <c r="E12" t="s">
-        <v>686</v>
+        <v>764</v>
       </c>
       <c r="F12" t="str">
         <f t="shared" si="0"/>
@@ -3476,15 +3460,15 @@
       </c>
       <c r="J12">
         <f t="shared" si="1"/>
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A13" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>321</v>
+        <v>378</v>
       </c>
       <c r="C13" s="2" t="str">
         <f>IFERROR(
@@ -3499,13 +3483,13 @@
   ),
   ""
 )</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D13" t="s">
         <v>24</v>
       </c>
       <c r="E13" t="s">
-        <v>687</v>
+        <v>765</v>
       </c>
       <c r="F13" t="str">
         <f t="shared" si="0"/>
@@ -3513,15 +3497,15 @@
       </c>
       <c r="J13">
         <f t="shared" si="1"/>
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A14" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>327</v>
+        <v>385</v>
       </c>
       <c r="C14" s="2" t="str">
         <f>IFERROR(
@@ -3536,13 +3520,13 @@
   ),
   ""
 )</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D14" t="s">
         <v>24</v>
       </c>
       <c r="E14" t="s">
-        <v>759</v>
+        <v>766</v>
       </c>
       <c r="F14" t="str">
         <f t="shared" si="0"/>
@@ -3550,15 +3534,15 @@
       </c>
       <c r="J14">
         <f t="shared" si="1"/>
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A15" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>333</v>
+        <v>393</v>
       </c>
       <c r="C15" s="2" t="str">
         <f>IFERROR(
@@ -3573,13 +3557,13 @@
   ),
   ""
 )</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D15" t="s">
         <v>24</v>
       </c>
       <c r="E15" t="s">
-        <v>756</v>
+        <v>767</v>
       </c>
       <c r="F15" t="str">
         <f t="shared" si="0"/>
@@ -3587,15 +3571,15 @@
       </c>
       <c r="J15">
         <f t="shared" si="1"/>
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A16" t="s">
-        <v>68</v>
+        <v>223</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>339</v>
+        <v>255</v>
       </c>
       <c r="C16" s="2" t="str">
         <f>IFERROR(
@@ -3616,7 +3600,7 @@
         <v>24</v>
       </c>
       <c r="E16" t="s">
-        <v>760</v>
+        <v>676</v>
       </c>
       <c r="F16" t="str">
         <f t="shared" si="0"/>
@@ -3624,15 +3608,15 @@
       </c>
       <c r="J16">
         <f t="shared" si="1"/>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A17" t="s">
-        <v>69</v>
+        <v>224</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>343</v>
+        <v>260</v>
       </c>
       <c r="C17" s="2" t="str">
         <f>IFERROR(
@@ -3653,7 +3637,7 @@
         <v>24</v>
       </c>
       <c r="E17" t="s">
-        <v>757</v>
+        <v>677</v>
       </c>
       <c r="F17" t="str">
         <f t="shared" si="0"/>
@@ -3661,15 +3645,15 @@
       </c>
       <c r="J17">
         <f t="shared" si="1"/>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A18" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>348</v>
+        <v>266</v>
       </c>
       <c r="C18" s="2" t="str">
         <f>IFERROR(
@@ -3684,13 +3668,13 @@
   ),
   ""
 )</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D18" t="s">
         <v>24</v>
       </c>
       <c r="E18" t="s">
-        <v>761</v>
+        <v>678</v>
       </c>
       <c r="F18" t="str">
         <f t="shared" si="0"/>
@@ -3698,15 +3682,15 @@
       </c>
       <c r="J18">
         <f t="shared" si="1"/>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A19" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>354</v>
+        <v>271</v>
       </c>
       <c r="C19" s="2" t="str">
         <f>IFERROR(
@@ -3721,13 +3705,13 @@
   ),
   ""
 )</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D19" t="s">
         <v>24</v>
       </c>
       <c r="E19" t="s">
-        <v>758</v>
+        <v>679</v>
       </c>
       <c r="F19" t="str">
         <f t="shared" si="0"/>
@@ -3735,15 +3719,15 @@
       </c>
       <c r="J19">
         <f t="shared" si="1"/>
-        <v>17</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A20" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>359</v>
+        <v>277</v>
       </c>
       <c r="C20" s="2" t="str">
         <f>IFERROR(
@@ -3758,13 +3742,13 @@
   ),
   ""
 )</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D20" t="s">
         <v>24</v>
       </c>
       <c r="E20" t="s">
-        <v>762</v>
+        <v>680</v>
       </c>
       <c r="F20" t="str">
         <f t="shared" si="0"/>
@@ -3772,15 +3756,15 @@
       </c>
       <c r="J20">
         <f t="shared" si="1"/>
-        <v>18</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A21" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>365</v>
+        <v>283</v>
       </c>
       <c r="C21" s="2" t="str">
         <f>IFERROR(
@@ -3795,13 +3779,13 @@
   ),
   ""
 )</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D21" t="s">
         <v>24</v>
       </c>
       <c r="E21" t="s">
-        <v>763</v>
+        <v>681</v>
       </c>
       <c r="F21" t="str">
         <f t="shared" si="0"/>
@@ -3809,15 +3793,15 @@
       </c>
       <c r="J21">
         <f t="shared" si="1"/>
-        <v>19</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A22" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>371</v>
+        <v>289</v>
       </c>
       <c r="C22" s="2" t="str">
         <f>IFERROR(
@@ -3832,13 +3816,13 @@
   ),
   ""
 )</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D22" t="s">
         <v>24</v>
       </c>
       <c r="E22" t="s">
-        <v>764</v>
+        <v>682</v>
       </c>
       <c r="F22" t="str">
         <f t="shared" si="0"/>
@@ -3846,15 +3830,15 @@
       </c>
       <c r="J22">
         <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.15">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A23" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>378</v>
+        <v>296</v>
       </c>
       <c r="C23" s="2" t="str">
         <f>IFERROR(
@@ -3869,13 +3853,13 @@
   ),
   ""
 )</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D23" t="s">
         <v>24</v>
       </c>
       <c r="E23" t="s">
-        <v>765</v>
+        <v>683</v>
       </c>
       <c r="F23" t="str">
         <f t="shared" si="0"/>
@@ -3883,15 +3867,15 @@
       </c>
       <c r="J23">
         <f t="shared" si="1"/>
-        <v>21</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.15">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A24" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>385</v>
+        <v>303</v>
       </c>
       <c r="C24" s="2" t="str">
         <f>IFERROR(
@@ -3906,13 +3890,13 @@
   ),
   ""
 )</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D24" t="s">
         <v>24</v>
       </c>
       <c r="E24" t="s">
-        <v>766</v>
+        <v>684</v>
       </c>
       <c r="F24" t="str">
         <f t="shared" si="0"/>
@@ -3920,15 +3904,15 @@
       </c>
       <c r="J24">
         <f t="shared" si="1"/>
-        <v>22</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.15">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A25" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>393</v>
+        <v>309</v>
       </c>
       <c r="C25" s="2" t="str">
         <f>IFERROR(
@@ -3943,13 +3927,13 @@
   ),
   ""
 )</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D25" t="s">
         <v>24</v>
       </c>
       <c r="E25" t="s">
-        <v>767</v>
+        <v>685</v>
       </c>
       <c r="F25" t="str">
         <f t="shared" si="0"/>
@@ -3957,7 +3941,7 @@
       </c>
       <c r="J25">
         <f t="shared" si="1"/>
-        <v>23</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
@@ -4110,9 +4094,11 @@
     </row>
     <row r="30" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A30" t="s">
-        <v>82</v>
-      </c>
-      <c r="B30" s="2"/>
+        <v>64</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>316</v>
+      </c>
       <c r="C30" s="2" t="str">
         <f>IFERROR(
   INDEX(Sheet1!$B$1:$N$1,
@@ -4126,13 +4112,13 @@
   ),
   ""
 )</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="D30" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="E30" t="s">
-        <v>833</v>
+        <v>686</v>
       </c>
       <c r="F30" t="str">
         <f t="shared" si="0"/>
@@ -4140,7 +4126,7 @@
       </c>
       <c r="J30">
         <f t="shared" si="1"/>
-        <v>28</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
@@ -4526,9 +4512,11 @@
     </row>
     <row r="42" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A42" t="s">
-        <v>94</v>
-      </c>
-      <c r="B42" s="2"/>
+        <v>65</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>321</v>
+      </c>
       <c r="C42" s="2" t="str">
         <f>IFERROR(
   INDEX(Sheet1!$B$1:$N$1,
@@ -4542,13 +4530,13 @@
   ),
   ""
 )</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="D42" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="E42" t="s">
-        <v>835</v>
+        <v>687</v>
       </c>
       <c r="F42" t="str">
         <f t="shared" si="2"/>
@@ -4556,7 +4544,7 @@
       </c>
       <c r="J42">
         <f t="shared" si="3"/>
-        <v>40</v>
+        <v>11</v>
       </c>
     </row>
     <row r="43" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
@@ -6513,9 +6501,11 @@
     </row>
     <row r="97" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A97" t="s">
-        <v>149</v>
-      </c>
-      <c r="B97" s="2"/>
+        <v>66</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>327</v>
+      </c>
       <c r="C97" s="2" t="str">
         <f>IFERROR(
   INDEX(Sheet1!$B$1:$N$1,
@@ -6529,13 +6519,13 @@
   ),
   ""
 )</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="D97" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="E97" t="s">
-        <v>830</v>
+        <v>759</v>
       </c>
       <c r="F97" t="str">
         <f t="shared" si="4"/>
@@ -6543,7 +6533,7 @@
       </c>
       <c r="J97">
         <f t="shared" si="5"/>
-        <v>95</v>
+        <v>12</v>
       </c>
     </row>
     <row r="98" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
@@ -6945,7 +6935,7 @@
     </row>
     <row r="109" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A109" t="s">
-        <v>161</v>
+        <v>193</v>
       </c>
       <c r="B109" s="2"/>
       <c r="C109" s="2" t="str">
@@ -6967,7 +6957,7 @@
         <v>9</v>
       </c>
       <c r="E109" t="s">
-        <v>818</v>
+        <v>797</v>
       </c>
       <c r="F109" t="str">
         <f t="shared" si="6"/>
@@ -6975,14 +6965,16 @@
       </c>
       <c r="J109">
         <f t="shared" si="7"/>
-        <v>107</v>
+        <v>139</v>
       </c>
     </row>
     <row r="110" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A110" t="s">
-        <v>162</v>
-      </c>
-      <c r="B110" s="2"/>
+        <v>67</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>333</v>
+      </c>
       <c r="C110" s="2" t="str">
         <f>IFERROR(
   INDEX(Sheet1!$B$1:$N$1,
@@ -6996,13 +6988,13 @@
   ),
   ""
 )</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="D110" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="E110" t="s">
-        <v>824</v>
+        <v>756</v>
       </c>
       <c r="F110" t="str">
         <f t="shared" si="6"/>
@@ -7010,14 +7002,16 @@
       </c>
       <c r="J110">
         <f t="shared" si="7"/>
-        <v>108</v>
+        <v>13</v>
       </c>
     </row>
     <row r="111" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A111" t="s">
-        <v>163</v>
-      </c>
-      <c r="B111" s="2"/>
+        <v>68</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>339</v>
+      </c>
       <c r="C111" s="2" t="str">
         <f>IFERROR(
   INDEX(Sheet1!$B$1:$N$1,
@@ -7031,13 +7025,13 @@
   ),
   ""
 )</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="D111" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="E111" t="s">
-        <v>825</v>
+        <v>760</v>
       </c>
       <c r="F111" t="str">
         <f t="shared" si="6"/>
@@ -7045,7 +7039,7 @@
       </c>
       <c r="J111">
         <f t="shared" si="7"/>
-        <v>109</v>
+        <v>14</v>
       </c>
     </row>
     <row r="112" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
@@ -7313,9 +7307,11 @@
     </row>
     <row r="119" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A119" t="s">
-        <v>171</v>
-      </c>
-      <c r="B119" s="2"/>
+        <v>69</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>343</v>
+      </c>
       <c r="C119" s="2" t="str">
         <f>IFERROR(
   INDEX(Sheet1!$B$1:$N$1,
@@ -7329,13 +7325,13 @@
   ),
   ""
 )</f>
-        <v/>
+        <v>1</v>
       </c>
       <c r="D119" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="E119" t="s">
-        <v>800</v>
+        <v>757</v>
       </c>
       <c r="F119" t="str">
         <f t="shared" si="6"/>
@@ -7343,12 +7339,12 @@
       </c>
       <c r="J119">
         <f t="shared" si="7"/>
-        <v>117</v>
+        <v>15</v>
       </c>
     </row>
     <row r="120" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A120" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="B120" s="2"/>
       <c r="C120" s="2" t="str">
@@ -7370,7 +7366,7 @@
         <v>9</v>
       </c>
       <c r="E120" t="s">
-        <v>798</v>
+        <v>818</v>
       </c>
       <c r="F120" t="str">
         <f t="shared" si="6"/>
@@ -7378,7 +7374,7 @@
       </c>
       <c r="J120">
         <f t="shared" si="7"/>
-        <v>118</v>
+        <v>107</v>
       </c>
     </row>
     <row r="121" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
@@ -7593,9 +7589,11 @@
     </row>
     <row r="127" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A127" t="s">
-        <v>179</v>
-      </c>
-      <c r="B127" s="2"/>
+        <v>70</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>348</v>
+      </c>
       <c r="C127" s="2" t="str">
         <f>IFERROR(
   INDEX(Sheet1!$B$1:$N$1,
@@ -7609,13 +7607,13 @@
   ),
   ""
 )</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="D127" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="E127" t="s">
-        <v>831</v>
+        <v>761</v>
       </c>
       <c r="F127" t="str">
         <f t="shared" si="6"/>
@@ -7623,7 +7621,7 @@
       </c>
       <c r="J127">
         <f t="shared" si="7"/>
-        <v>125</v>
+        <v>16</v>
       </c>
     </row>
     <row r="128" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
@@ -8118,7 +8116,7 @@
     </row>
     <row r="141" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A141" t="s">
-        <v>193</v>
+        <v>172</v>
       </c>
       <c r="B141" s="2"/>
       <c r="C141" s="2" t="str">
@@ -8140,7 +8138,7 @@
         <v>9</v>
       </c>
       <c r="E141" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="F141" t="str">
         <f t="shared" si="8"/>
@@ -8148,7 +8146,7 @@
       </c>
       <c r="J141">
         <f t="shared" si="9"/>
-        <v>139</v>
+        <v>118</v>
       </c>
     </row>
     <row r="142" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
@@ -8219,7 +8217,7 @@
         <v>No</v>
       </c>
       <c r="J144">
-        <f t="shared" ref="J144:J171" si="10">IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(A144,"GPIO",""),"号","")),"")</f>
+        <f t="shared" ref="J144:J154" si="10">IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(A144,"GPIO",""),"号","")),"")</f>
         <v>142</v>
       </c>
     </row>
@@ -8569,9 +8567,11 @@
     </row>
     <row r="154" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A154" t="s">
-        <v>206</v>
-      </c>
-      <c r="B154" s="2"/>
+        <v>71</v>
+      </c>
+      <c r="B154" s="2" t="s">
+        <v>354</v>
+      </c>
       <c r="C154" s="2" t="str">
         <f>IFERROR(
   INDEX(Sheet1!$B$1:$N$1,
@@ -8585,13 +8585,13 @@
   ),
   ""
 )</f>
-        <v/>
+        <v>5</v>
       </c>
       <c r="D154" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="E154" t="s">
-        <v>799</v>
+        <v>758</v>
       </c>
       <c r="F154" t="str">
         <f t="shared" si="8"/>
@@ -8599,7 +8599,7 @@
       </c>
       <c r="J154">
         <f t="shared" si="10"/>
-        <v>152</v>
+        <v>17</v>
       </c>
     </row>
     <row r="155" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
@@ -8623,11 +8623,11 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="F155:F161" si="11">IF(E155&lt;&gt;"","Yes","No")</f>
         <v>No</v>
       </c>
       <c r="J155">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="J155:J171" si="12">IFERROR(VALUE(SUBSTITUTE(SUBSTITUTE(A155,"GPIO",""),"号","")),"")</f>
         <v>153</v>
       </c>
     </row>
@@ -8652,11 +8652,11 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>No</v>
       </c>
       <c r="J156">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>154</v>
       </c>
     </row>
@@ -8681,11 +8681,11 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>No</v>
       </c>
       <c r="J157">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>155</v>
       </c>
     </row>
@@ -8718,14 +8718,14 @@
         <v>694</v>
       </c>
       <c r="F158" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>Yes</v>
       </c>
       <c r="G158" t="s">
         <v>770</v>
       </c>
       <c r="J158">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>156</v>
       </c>
     </row>
@@ -8756,11 +8756,11 @@
         <v>821</v>
       </c>
       <c r="F159" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>Yes</v>
       </c>
       <c r="J159">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>157</v>
       </c>
     </row>
@@ -8785,11 +8785,11 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>No</v>
       </c>
       <c r="J160">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>158</v>
       </c>
     </row>
@@ -8822,14 +8822,14 @@
         <v>695</v>
       </c>
       <c r="F161" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>Yes</v>
       </c>
       <c r="G161" t="s">
         <v>770</v>
       </c>
       <c r="J161">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>159</v>
       </c>
     </row>
@@ -8862,14 +8862,14 @@
         <v>696</v>
       </c>
       <c r="F162" t="str">
-        <f t="shared" ref="F162:F193" si="11">IF(E162&lt;&gt;"","Yes","No")</f>
+        <f t="shared" ref="F162:F191" si="13">IF(E162&lt;&gt;"","Yes","No")</f>
         <v>Yes</v>
       </c>
       <c r="G162" t="s">
         <v>770</v>
       </c>
       <c r="J162">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>160</v>
       </c>
     </row>
@@ -8902,14 +8902,14 @@
         <v>697</v>
       </c>
       <c r="F163" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>Yes</v>
       </c>
       <c r="G163" t="s">
         <v>770</v>
       </c>
       <c r="J163">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>161</v>
       </c>
     </row>
@@ -8934,11 +8934,11 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>No</v>
       </c>
       <c r="J164">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>162</v>
       </c>
     </row>
@@ -8963,11 +8963,11 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>No</v>
       </c>
       <c r="J165">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>163</v>
       </c>
     </row>
@@ -8992,11 +8992,11 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>No</v>
       </c>
       <c r="J166">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>164</v>
       </c>
     </row>
@@ -9021,11 +9021,11 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>No</v>
       </c>
       <c r="J167">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>165</v>
       </c>
     </row>
@@ -9056,11 +9056,11 @@
         <v>804</v>
       </c>
       <c r="F168" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>Yes</v>
       </c>
       <c r="J168">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>166</v>
       </c>
     </row>
@@ -9091,11 +9091,11 @@
         <v>811</v>
       </c>
       <c r="F169" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>Yes</v>
       </c>
       <c r="J169">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>167</v>
       </c>
     </row>
@@ -9126,11 +9126,11 @@
         <v>803</v>
       </c>
       <c r="F170" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>Yes</v>
       </c>
       <c r="J170">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>168</v>
       </c>
     </row>
@@ -9142,11 +9142,11 @@
         <v>17</v>
       </c>
       <c r="F171" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>No</v>
       </c>
       <c r="J171" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v/>
       </c>
     </row>
@@ -9158,7 +9158,7 @@
         <v>17</v>
       </c>
       <c r="F172" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>No</v>
       </c>
     </row>
@@ -9170,7 +9170,7 @@
         <v>17</v>
       </c>
       <c r="F173" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>No</v>
       </c>
     </row>
@@ -9182,7 +9182,7 @@
         <v>17</v>
       </c>
       <c r="F174" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>No</v>
       </c>
     </row>
@@ -9194,7 +9194,7 @@
         <v>17</v>
       </c>
       <c r="F175" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>No</v>
       </c>
     </row>
@@ -9206,7 +9206,7 @@
         <v>17</v>
       </c>
       <c r="F176" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>No</v>
       </c>
     </row>
@@ -9218,7 +9218,7 @@
         <v>17</v>
       </c>
       <c r="F177" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>No</v>
       </c>
     </row>
@@ -9230,7 +9230,7 @@
         <v>17</v>
       </c>
       <c r="F178" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>No</v>
       </c>
     </row>
@@ -9242,7 +9242,7 @@
         <v>17</v>
       </c>
       <c r="F179" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>No</v>
       </c>
     </row>
@@ -9254,7 +9254,7 @@
         <v>17</v>
       </c>
       <c r="F180" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>No</v>
       </c>
     </row>
@@ -9266,7 +9266,7 @@
         <v>17</v>
       </c>
       <c r="F181" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>No</v>
       </c>
     </row>
@@ -9278,7 +9278,7 @@
         <v>17</v>
       </c>
       <c r="F182" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>No</v>
       </c>
     </row>
@@ -9290,7 +9290,7 @@
         <v>17</v>
       </c>
       <c r="F183" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>No</v>
       </c>
     </row>
@@ -9302,7 +9302,7 @@
         <v>17</v>
       </c>
       <c r="F184" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>No</v>
       </c>
     </row>
@@ -9314,7 +9314,7 @@
         <v>17</v>
       </c>
       <c r="F185" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>No</v>
       </c>
     </row>
@@ -9326,7 +9326,7 @@
         <v>17</v>
       </c>
       <c r="F186" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>No</v>
       </c>
     </row>
@@ -9338,7 +9338,7 @@
         <v>17</v>
       </c>
       <c r="F187" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>No</v>
       </c>
     </row>
@@ -9350,7 +9350,7 @@
         <v>17</v>
       </c>
       <c r="F188" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>No</v>
       </c>
     </row>
@@ -9362,7 +9362,7 @@
         <v>17</v>
       </c>
       <c r="F189" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>No</v>
       </c>
     </row>
@@ -9374,7 +9374,7 @@
         <v>17</v>
       </c>
       <c r="F190" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>No</v>
       </c>
     </row>
@@ -9386,19 +9386,22 @@
         <v>17</v>
       </c>
       <c r="F191" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>No</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:J191" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="3">
+    <filterColumn colId="4">
       <filters>
-        <filter val="PWM"/>
+        <filter val="DSP_PWM1~{_ENABLE}"/>
+        <filter val="DSP_PWM2~{_ENABLE}"/>
+        <filter val="DSP_PWM3~{_ENABLE}"/>
+        <filter val="DSP_PWM4~{_ENABLE}"/>
       </filters>
     </filterColumn>
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J191">
-      <sortCondition ref="J1:J191"/>
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A109:J141">
+      <sortCondition ref="E1:E191"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/28388motherboard/TMS320F28388D_PinMap.xlsx
+++ b/28388motherboard/TMS320F28388D_PinMap.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\codefile\28388Board\mmlab-12PhaseDrive-388Slave\28388motherboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{597D13C1-D3F8-4A04-8052-750172845AA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBBB2D64-020C-4250-96F9-4AE553E1F059}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="38700" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PinMap" sheetId="1" r:id="rId1"/>
@@ -3107,7 +3107,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>94</v>
       </c>
@@ -3177,7 +3177,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
         <v>162</v>
       </c>
@@ -3247,7 +3247,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
         <v>149</v>
       </c>
@@ -3317,7 +3317,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
         <v>82</v>
       </c>
@@ -7476,7 +7476,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="124" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A124" t="s">
         <v>176</v>
       </c>
@@ -7513,7 +7513,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="125" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A125" t="s">
         <v>177</v>
       </c>
@@ -7550,7 +7550,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="126" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A126" t="s">
         <v>178</v>
       </c>
@@ -7624,7 +7624,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="128" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A128" t="s">
         <v>180</v>
       </c>
@@ -7699,7 +7699,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="130" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="130" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A130" t="s">
         <v>182</v>
       </c>
@@ -7728,7 +7728,7 @@
         <v>791</v>
       </c>
       <c r="F130" t="str">
-        <f t="shared" ref="F130:F161" si="8">IF(E130&lt;&gt;"","Yes","No")</f>
+        <f t="shared" ref="F130:F154" si="8">IF(E130&lt;&gt;"","Yes","No")</f>
         <v>Yes</v>
       </c>
       <c r="G130" t="s">
@@ -7774,7 +7774,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="132" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="132" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A132" t="s">
         <v>184</v>
       </c>
@@ -7811,7 +7811,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="133" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="133" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A133" t="s">
         <v>185</v>
       </c>
@@ -7848,7 +7848,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="134" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="134" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A134" t="s">
         <v>186</v>
       </c>
@@ -7920,7 +7920,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="136" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="136" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A136" t="s">
         <v>188</v>
       </c>
@@ -8000,7 +8000,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="138" spans="1:10" hidden="1" x14ac:dyDescent="0.15">
+    <row r="138" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A138" t="s">
         <v>190</v>
       </c>
@@ -9392,12 +9392,9 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:J191" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="4">
+    <filterColumn colId="3">
       <filters>
-        <filter val="DSP_PWM1~{_ENABLE}"/>
-        <filter val="DSP_PWM2~{_ENABLE}"/>
-        <filter val="DSP_PWM3~{_ENABLE}"/>
-        <filter val="DSP_PWM4~{_ENABLE}"/>
+        <filter val="SDFM"/>
       </filters>
     </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A109:J141">
